--- a/archive/REM - Vsense.xlsx
+++ b/archive/REM - Vsense.xlsx
@@ -8,15 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/margabudi/Documents/hardware/ESU/archive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035178B6-BCC1-A345-B8DD-468272214C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2ED8972-4586-9A4E-803D-28292FB1E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet4!$B$3:$B$23</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet4!$C$2</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet4!$C$3:$C$23</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet4!$B$2</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet4!$B$3:$B$23</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet4!$C$2</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet4!$C$3:$C$23</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,12 +45,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="14">
   <si>
     <t>R</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>V</t>
     </r>
     <r>
@@ -49,7 +66,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>RMS</t>
@@ -57,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>V</t>
     </r>
     <r>
@@ -65,7 +89,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>max</t>
@@ -73,6 +97,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>V</t>
     </r>
     <r>
@@ -81,17 +112,17 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>min</t>
     </r>
   </si>
   <si>
-    <t>ADC</t>
+    <t>Swing</t>
   </si>
   <si>
-    <t>Swing</t>
+    <t>ADC</t>
   </si>
   <si>
     <t>High Z</t>
@@ -114,17 +145,27 @@
   <si>
     <t>w/</t>
   </si>
+  <si>
+    <t>REM Test Results Under Varying Input Resistance</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0000_ "/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0000000000000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000_ "/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,7 +178,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -170,29 +211,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,7 +490,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -482,7 +526,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -703,7 +747,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A132-4B44-A1BB-92CA89745EFA}"/>
+              <c16:uniqueId val="{00000001-5C3D-9049-BAE8-06B7D9ACF873}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -897,7 +941,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9BA6-EE4E-AC5A-A5AD3CFD6376}"/>
+              <c16:uniqueId val="{00000003-5C3D-9049-BAE8-06B7D9ACF873}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1100,7 +1144,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-9BA6-EE4E-AC5A-A5AD3CFD6376}"/>
+              <c16:uniqueId val="{00000005-5C3D-9049-BAE8-06B7D9ACF873}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1173,7 +1217,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1238,7 +1282,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1268,6 +1312,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{f462f681-6c57-4df1-81e6-f8661d0b17ef}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1289,7 +1338,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr lang="en-US"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -1323,7 +1372,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1359,7 +1408,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1512,67 +1561,67 @@
                 <c:formatCode>0.0000_ </c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.3399999999999874E-2</c:v>
+                  <c:v>3.3399999999999902E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.30659999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.43270000000000008</c:v>
+                  <c:v>0.43269999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.50170000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.54280000000000017</c:v>
+                  <c:v>0.54279999999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.57189999999999985</c:v>
+                  <c:v>0.57189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.59089999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.60490000000000022</c:v>
+                  <c:v>0.60489999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.61660000000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.62579999999999991</c:v>
+                  <c:v>0.62580000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.63379999999999992</c:v>
+                  <c:v>0.63380000000000003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.64029999999999987</c:v>
+                  <c:v>0.64029999999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.64559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6503000000000001</c:v>
+                  <c:v>0.65029999999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.65450000000000008</c:v>
+                  <c:v>0.65449999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.6581999999999999</c:v>
+                  <c:v>0.65820000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.66089999999999982</c:v>
+                  <c:v>0.66090000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.6633</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.6655000000000002</c:v>
+                  <c:v>0.66549999999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.66820000000000013</c:v>
+                  <c:v>0.66820000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.67019999999999991</c:v>
+                  <c:v>0.67020000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1580,7 +1629,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D4B3-DD4A-8C0B-BDE4B9AA3FCC}"/>
+              <c16:uniqueId val="{00000001-5608-4E46-B3C3-F802B661FBE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1715,22 +1764,22 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>8.7000000000001521E-3</c:v>
+                  <c:v>8.7000000000001503E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25760000000000005</c:v>
+                  <c:v>0.2576</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.37020000000000008</c:v>
+                  <c:v>0.37019999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4262999999999999</c:v>
+                  <c:v>0.42630000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.46499999999999986</c:v>
+                  <c:v>0.46500000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.48890000000000011</c:v>
+                  <c:v>0.4889</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.50590000000000002</c:v>
@@ -1739,7 +1788,7 @@
                   <c:v>0.51980000000000004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.53120000000000012</c:v>
+                  <c:v>0.53120000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.54020000000000001</c:v>
@@ -1748,22 +1797,22 @@
                   <c:v>0.54630000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.55160000000000009</c:v>
+                  <c:v>0.55159999999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.55650000000000022</c:v>
+                  <c:v>0.55649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.56009999999999982</c:v>
+                  <c:v>0.56010000000000004</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.56579999999999986</c:v>
+                  <c:v>0.56579999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.56740000000000013</c:v>
+                  <c:v>0.56740000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.5714999999999999</c:v>
+                  <c:v>0.57150000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0.57279999999999998</c:v>
@@ -1774,7 +1823,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D4B3-DD4A-8C0B-BDE4B9AA3FCC}"/>
+              <c16:uniqueId val="{00000003-5608-4E46-B3C3-F802B661FBE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1909,10 +1958,10 @@
                 <c:formatCode>0.0000_ </c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>5.1699999999999857E-2</c:v>
+                  <c:v>5.1699999999999899E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.37360000000000015</c:v>
+                  <c:v>0.37359999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.51239999999999997</c:v>
@@ -1921,49 +1970,49 @@
                   <c:v>0.58689999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.63249999999999984</c:v>
+                  <c:v>0.63249999999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.66210000000000013</c:v>
+                  <c:v>0.66210000000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.68449999999999989</c:v>
+                  <c:v>0.6845</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6987000000000001</c:v>
+                  <c:v>0.69869999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.70979999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.71700000000000008</c:v>
+                  <c:v>0.71699999999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.72319999999999984</c:v>
+                  <c:v>0.72319999999999995</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.72889999999999988</c:v>
+                  <c:v>0.72889999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.73280000000000012</c:v>
+                  <c:v>0.73280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.73579999999999979</c:v>
+                  <c:v>0.73580000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.73850000000000016</c:v>
+                  <c:v>0.73850000000000005</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.74069999999999991</c:v>
+                  <c:v>0.74070000000000003</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.74359999999999982</c:v>
+                  <c:v>0.74360000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.74449999999999994</c:v>
+                  <c:v>0.74450000000000005</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.7448999999999999</c:v>
+                  <c:v>0.74490000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.74639999999999995</c:v>
@@ -1977,7 +2026,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-D4B3-DD4A-8C0B-BDE4B9AA3FCC}"/>
+              <c16:uniqueId val="{00000005-5608-4E46-B3C3-F802B661FBE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2050,7 +2099,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2114,7 +2163,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2132,6 +2181,543 @@
         <c:crossAx val="1112763776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{d95250b8-4e0c-4c79-9b35-57f76fae58f7}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VRMS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet4!$B$3:$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet4!$C$3:$C$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>1.9E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3982</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78859999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1043000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3263</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5224</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6637999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7959000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8996999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9927999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0655000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1444000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2038000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2563</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3071000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3546</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3933</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4276</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4626999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4944000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5204</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5549-9440-880A-6851A07CEDA2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2054039616"/>
+        <c:axId val="2054037824"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2054039616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Resistance [Ω]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054037824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054037824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Voltage [V]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054039616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
+        <c:minorUnit val="0.1"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2258,6 +2844,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2775,6 +3401,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3310,7 +4452,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C660991-A648-1441-35CB-D491F58150C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3351,13 +4493,52 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE9D1C8-1943-5040-8335-805E84228D57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>679623</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>185351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>679623</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>6864</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A59C0DB-8F25-4783-3BB0-D2518CB5242B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3635,17 +4816,17 @@
   <dimension ref="B1:P74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C1" s="1">
         <v>100</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="4">
         <f>AVERAGE(G3:G23)</f>
-        <v>4.3657142857142874E-2</v>
+        <v>4.3657142857142901E-2</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="17" x14ac:dyDescent="0.2">
@@ -3662,500 +4843,500 @@
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>0</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>2.0333999999999999</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="4">
         <v>2.0722999999999998</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>1.9874000000000001</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G23" si="0">MAX((E3-D3),(D3-F3))</f>
-        <v>4.5999999999999819E-2</v>
+        <v>4.5999999999999798E-2</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>10</v>
       </c>
-      <c r="C4" s="2">
-        <f>1/((1/C$1)+(1/$B4))</f>
-        <v>9.0909090909090917</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="4">
+        <f t="shared" ref="C4:C23" si="1">1/((1/C$1)+(1/$B4))</f>
+        <v>9.0909090909090899</v>
+      </c>
+      <c r="D4" s="4">
         <v>2.3066</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="4">
         <v>2.3422999999999998</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>2.2652000000000001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>4.1399999999999881E-2</v>
+        <v>4.1399999999999902E-2</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>20</v>
       </c>
-      <c r="C5" s="2">
-        <f>1/((1/C$1)+(1/$B5))</f>
-        <v>16.666666666666664</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5" s="4">
+        <f t="shared" si="1"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="D5" s="4">
         <v>2.4327000000000001</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="4">
         <v>2.4666999999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>2.3839999999999999</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>4.8700000000000188E-2</v>
-      </c>
-      <c r="H5" s="3"/>
+        <v>4.8700000000000201E-2</v>
+      </c>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>30</v>
       </c>
-      <c r="C6" s="2">
-        <f>1/((1/C$1)+(1/$B6))</f>
-        <v>23.076923076923077</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6" s="4">
+        <f t="shared" si="1"/>
+        <v>23.076923076923102</v>
+      </c>
+      <c r="D6" s="4">
         <v>2.5017</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="4">
         <v>2.5400999999999998</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>2.4559000000000002</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>4.5799999999999841E-2</v>
-      </c>
-      <c r="H6" s="3"/>
+        <v>4.5799999999999799E-2</v>
+      </c>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>40</v>
       </c>
-      <c r="C7" s="2">
-        <f>1/((1/C$1)+(1/$B7))</f>
-        <v>28.571428571428569</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="4">
+        <f t="shared" si="1"/>
+        <v>28.571428571428601</v>
+      </c>
+      <c r="D7" s="4">
         <v>2.5428000000000002</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="4">
         <v>2.5808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>2.5032999999999999</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>3.9500000000000313E-2</v>
-      </c>
-      <c r="H7" s="3"/>
+        <v>3.9500000000000299E-2</v>
+      </c>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>50</v>
       </c>
-      <c r="C8" s="2">
-        <f>1/((1/C$1)+(1/$B8))</f>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="C8" s="4">
+        <f t="shared" si="1"/>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D8" s="4">
         <v>2.5718999999999999</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="4">
         <v>2.6071</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>2.5303</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>4.1599999999999859E-2</v>
-      </c>
-      <c r="H8" s="3"/>
+        <v>4.1599999999999901E-2</v>
+      </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>60</v>
       </c>
-      <c r="C9" s="2">
-        <f>1/((1/C$1)+(1/$B9))</f>
+      <c r="C9" s="4">
+        <f t="shared" si="1"/>
         <v>37.5</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="4">
         <v>2.5909</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="4">
         <v>2.625</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>2.5497000000000001</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="4">
         <f t="shared" si="0"/>
         <v>4.1199999999999903E-2</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>70</v>
       </c>
-      <c r="C10" s="2">
-        <f>1/((1/C$1)+(1/$B10))</f>
+      <c r="C10" s="4">
+        <f t="shared" si="1"/>
         <v>41.176470588235297</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="4">
         <v>2.6049000000000002</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="4">
         <v>2.6427</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>2.5653999999999999</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="4">
         <f t="shared" si="0"/>
-        <v>3.9500000000000313E-2</v>
-      </c>
-      <c r="H10" s="3"/>
+        <v>3.9500000000000299E-2</v>
+      </c>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>80</v>
       </c>
-      <c r="C11" s="2">
-        <f>1/((1/C$1)+(1/$B11))</f>
-        <v>44.444444444444443</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="C11" s="4">
+        <f t="shared" si="1"/>
+        <v>44.4444444444444</v>
+      </c>
+      <c r="D11" s="4">
         <v>2.6166</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="4">
         <v>2.6526999999999998</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>2.5720000000000001</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="4">
         <f t="shared" si="0"/>
-        <v>4.4599999999999973E-2</v>
-      </c>
-      <c r="H11" s="3"/>
+        <v>4.4600000000000001E-2</v>
+      </c>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>90</v>
       </c>
-      <c r="C12" s="2">
-        <f>1/((1/C$1)+(1/$B12))</f>
-        <v>47.368421052631575</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="C12" s="4">
+        <f t="shared" si="1"/>
+        <v>47.368421052631597</v>
+      </c>
+      <c r="D12" s="4">
         <v>2.6257999999999999</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="4">
         <v>2.6608000000000001</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>2.5859999999999999</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="4">
         <f t="shared" si="0"/>
-        <v>3.9800000000000058E-2</v>
-      </c>
-      <c r="H12" s="3"/>
+        <v>3.9800000000000099E-2</v>
+      </c>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>100</v>
       </c>
-      <c r="C13" s="2">
-        <f>1/((1/C$1)+(1/$B13))</f>
+      <c r="C13" s="4">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="4">
         <v>2.6337999999999999</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="4">
         <v>2.6709000000000001</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>2.5897000000000001</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="4">
         <f t="shared" si="0"/>
-        <v>4.4099999999999806E-2</v>
-      </c>
-      <c r="H13" s="3"/>
+        <v>4.4099999999999799E-2</v>
+      </c>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>110</v>
       </c>
-      <c r="C14" s="2">
-        <f>1/((1/C$1)+(1/$B14))</f>
-        <v>52.380952380952387</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="C14" s="4">
+        <f t="shared" si="1"/>
+        <v>52.380952380952401</v>
+      </c>
+      <c r="D14" s="4">
         <v>2.6402999999999999</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="4">
         <v>2.6791999999999998</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>2.6013999999999999</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="4">
         <f t="shared" si="0"/>
-        <v>3.8899999999999935E-2</v>
-      </c>
-      <c r="H14" s="3"/>
+        <v>3.88999999999999E-2</v>
+      </c>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>120</v>
       </c>
-      <c r="C15" s="2">
-        <f>1/((1/C$1)+(1/$B15))</f>
-        <v>54.545454545454547</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="C15" s="4">
+        <f t="shared" si="1"/>
+        <v>54.545454545454497</v>
+      </c>
+      <c r="D15" s="4">
         <v>2.6456</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="4">
         <v>2.6854</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>2.6019000000000001</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="4">
         <f t="shared" si="0"/>
-        <v>4.369999999999985E-2</v>
-      </c>
-      <c r="H15" s="3"/>
+        <v>4.3699999999999899E-2</v>
+      </c>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>130</v>
       </c>
-      <c r="C16" s="2">
-        <f>1/((1/C$1)+(1/$B16))</f>
-        <v>56.521739130434774</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="C16" s="4">
+        <f t="shared" si="1"/>
+        <v>56.521739130434803</v>
+      </c>
+      <c r="D16" s="4">
         <v>2.6503000000000001</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="4">
         <v>2.6924999999999999</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>2.6996000000000002</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="4">
         <f t="shared" si="0"/>
-        <v>4.2199999999999793E-2</v>
-      </c>
-      <c r="H16" s="3"/>
+        <v>4.21999999999998E-2</v>
+      </c>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>140</v>
       </c>
-      <c r="C17" s="2">
-        <f>1/((1/C$1)+(1/$B17))</f>
-        <v>58.333333333333329</v>
-      </c>
-      <c r="D17" s="2">
+      <c r="C17" s="4">
+        <f t="shared" si="1"/>
+        <v>58.3333333333333</v>
+      </c>
+      <c r="D17" s="4">
         <v>2.6545000000000001</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="4">
         <v>2.6926999999999999</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>2.6105</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="4">
         <f t="shared" si="0"/>
-        <v>4.4000000000000039E-2</v>
-      </c>
-      <c r="H17" s="3"/>
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>150</v>
       </c>
-      <c r="C18" s="2">
-        <f>1/((1/C$1)+(1/$B18))</f>
+      <c r="C18" s="4">
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="4">
         <v>2.6581999999999999</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="4">
         <v>2.6959</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>2.6189</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="4">
         <f t="shared" si="0"/>
-        <v>3.9299999999999891E-2</v>
-      </c>
-      <c r="H18" s="3"/>
+        <v>3.9299999999999898E-2</v>
+      </c>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>160</v>
       </c>
-      <c r="C19" s="2">
-        <f>1/((1/C$1)+(1/$B19))</f>
-        <v>61.538461538461533</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="C19" s="4">
+        <f t="shared" si="1"/>
+        <v>61.538461538461497</v>
+      </c>
+      <c r="D19" s="4">
         <v>2.6608999999999998</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="4">
         <v>2.7042999999999999</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>2.6183999999999998</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="4">
         <f t="shared" si="0"/>
-        <v>4.3400000000000105E-2</v>
-      </c>
-      <c r="H19" s="3"/>
+        <v>4.3400000000000098E-2</v>
+      </c>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>170</v>
       </c>
-      <c r="C20" s="2">
-        <f>1/((1/C$1)+(1/$B20))</f>
-        <v>62.962962962962955</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C20" s="4">
+        <f t="shared" si="1"/>
+        <v>62.962962962962997</v>
+      </c>
+      <c r="D20" s="4">
         <v>2.6633</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="4">
         <v>2.6991000000000001</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>2.6141999999999999</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="4">
         <f t="shared" si="0"/>
-        <v>4.9100000000000144E-2</v>
-      </c>
-      <c r="H20" s="3"/>
+        <v>4.9100000000000102E-2</v>
+      </c>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>180</v>
       </c>
-      <c r="C21" s="2">
-        <f>1/((1/C$1)+(1/$B21))</f>
-        <v>64.285714285714292</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="C21" s="4">
+        <f t="shared" si="1"/>
+        <v>64.285714285714306</v>
+      </c>
+      <c r="D21" s="4">
         <v>2.6655000000000002</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="4">
         <v>2.7054999999999998</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>2.6189</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="4">
         <f t="shared" si="0"/>
         <v>4.6600000000000197E-2</v>
       </c>
-      <c r="H21" s="3"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>190</v>
       </c>
-      <c r="C22" s="2">
-        <f>1/((1/C$1)+(1/$B22))</f>
-        <v>65.517241379310335</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="C22" s="4">
+        <f t="shared" si="1"/>
+        <v>65.517241379310306</v>
+      </c>
+      <c r="D22" s="4">
         <v>2.6682000000000001</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="4">
         <v>2.7080000000000002</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>2.6208</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="4">
         <f t="shared" si="0"/>
-        <v>4.7400000000000109E-2</v>
-      </c>
-      <c r="H22" s="3"/>
+        <v>4.7400000000000102E-2</v>
+      </c>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>200</v>
       </c>
-      <c r="C23" s="2">
-        <f>1/((1/C$1)+(1/$B23))</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="C23" s="4">
+        <f t="shared" si="1"/>
+        <v>66.6666666666667</v>
+      </c>
+      <c r="D23" s="4">
         <v>2.6701999999999999</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="4">
         <v>2.7202000000000002</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="4">
         <v>2.6316000000000002</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="4">
         <f t="shared" si="0"/>
-        <v>5.0000000000000266E-2</v>
-      </c>
-      <c r="H23" s="3"/>
+        <v>5.0000000000000301E-2</v>
+      </c>
+      <c r="H23" s="5"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G25" s="2"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C26" s="1">
         <v>50</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="4">
         <f>AVERAGE(G28:G45)</f>
-        <v>1.6227777777777754E-2</v>
+        <v>1.6227777777777799E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="17" x14ac:dyDescent="0.2">
@@ -4171,419 +5352,419 @@
       <c r="F27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>0</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="3">
+      <c r="C28" s="4"/>
+      <c r="D28" s="5">
         <v>2.0087000000000002</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="5">
         <v>2.0209000000000001</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="5">
         <v>1.9922</v>
       </c>
-      <c r="G28" s="2">
-        <f t="shared" ref="G28:G48" si="1">MAX((E28-D28),(D28-F28))</f>
-        <v>1.6500000000000181E-2</v>
+      <c r="G28" s="4">
+        <f t="shared" ref="G28:G48" si="2">MAX((E28-D28),(D28-F28))</f>
+        <v>1.6500000000000199E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>10</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="4">
         <f>1/((1/C$26)+(1/$B29))</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="D29" s="3">
+        <v>8.3333333333333304</v>
+      </c>
+      <c r="D29" s="5">
         <v>2.2576000000000001</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="5">
         <v>2.2719999999999998</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="5">
         <v>2.2450000000000001</v>
       </c>
-      <c r="G29" s="2">
-        <f t="shared" si="1"/>
-        <v>1.4399999999999746E-2</v>
+      <c r="G29" s="4">
+        <f t="shared" si="2"/>
+        <v>1.4399999999999699E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>20</v>
       </c>
-      <c r="C30" s="2">
-        <f t="shared" ref="C30:C48" si="2">1/((1/C$26)+(1/$B30))</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="D30" s="3">
+      <c r="C30" s="4">
+        <f t="shared" ref="C30:C48" si="3">1/((1/C$26)+(1/$B30))</f>
+        <v>14.285714285714301</v>
+      </c>
+      <c r="D30" s="5">
         <v>2.3702000000000001</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="5">
         <v>2.3845999999999998</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="5">
         <v>2.3591000000000002</v>
       </c>
-      <c r="G30" s="2">
-        <f t="shared" si="1"/>
-        <v>1.4399999999999746E-2</v>
+      <c r="G30" s="4">
+        <f t="shared" si="2"/>
+        <v>1.4399999999999699E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>30</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="4">
+        <f t="shared" si="3"/>
+        <v>18.75</v>
+      </c>
+      <c r="D31" s="5">
+        <v>2.4262999999999999</v>
+      </c>
+      <c r="E31" s="5">
+        <v>2.4418000000000002</v>
+      </c>
+      <c r="F31" s="5">
+        <v>2.4131999999999998</v>
+      </c>
+      <c r="G31" s="4">
         <f t="shared" si="2"/>
-        <v>18.75</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2.4262999999999999</v>
-      </c>
-      <c r="E31" s="3">
-        <v>2.4418000000000002</v>
-      </c>
-      <c r="F31" s="3">
-        <v>2.4131999999999998</v>
-      </c>
-      <c r="G31" s="2">
-        <f t="shared" si="1"/>
-        <v>1.5500000000000291E-2</v>
+        <v>1.55000000000003E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>40</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="4">
+        <f t="shared" si="3"/>
+        <v>22.2222222222222</v>
+      </c>
+      <c r="D32" s="5">
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2.4851999999999999</v>
+      </c>
+      <c r="F32" s="5">
+        <v>2.4519000000000002</v>
+      </c>
+      <c r="G32" s="4">
         <f t="shared" si="2"/>
-        <v>22.222222222222221</v>
-      </c>
-      <c r="D32" s="3">
-        <v>2.4649999999999999</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2.4851999999999999</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2.4519000000000002</v>
-      </c>
-      <c r="G32" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0199999999999996E-2</v>
+        <v>2.0199999999999999E-2</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>50</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="4">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="D33" s="5">
+        <v>2.4889000000000001</v>
+      </c>
+      <c r="E33" s="5">
+        <v>2.5017</v>
+      </c>
+      <c r="F33" s="5">
+        <v>2.4763999999999999</v>
+      </c>
+      <c r="G33" s="4">
         <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-      <c r="D33" s="3">
-        <v>2.4889000000000001</v>
-      </c>
-      <c r="E33" s="3">
-        <v>2.5017</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2.4763999999999999</v>
-      </c>
-      <c r="G33" s="2">
-        <f t="shared" si="1"/>
-        <v>1.2799999999999923E-2</v>
+        <v>1.27999999999999E-2</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>60</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="4">
+        <f t="shared" si="3"/>
+        <v>27.272727272727298</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2.5059</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2.5217999999999998</v>
+      </c>
+      <c r="F34" s="5">
+        <v>2.4921000000000002</v>
+      </c>
+      <c r="G34" s="4">
         <f t="shared" si="2"/>
-        <v>27.272727272727273</v>
-      </c>
-      <c r="D34" s="3">
-        <v>2.5059</v>
-      </c>
-      <c r="E34" s="3">
-        <v>2.5217999999999998</v>
-      </c>
-      <c r="F34" s="3">
-        <v>2.4921000000000002</v>
-      </c>
-      <c r="G34" s="2">
-        <f t="shared" si="1"/>
-        <v>1.5899999999999803E-2</v>
+        <v>1.58999999999998E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>70</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="4">
+        <f t="shared" si="3"/>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="D35" s="5">
+        <v>2.5198</v>
+      </c>
+      <c r="E35" s="5">
+        <v>2.5341</v>
+      </c>
+      <c r="F35" s="5">
+        <v>2.5076000000000001</v>
+      </c>
+      <c r="G35" s="4">
         <f t="shared" si="2"/>
-        <v>29.166666666666664</v>
-      </c>
-      <c r="D35" s="3">
-        <v>2.5198</v>
-      </c>
-      <c r="E35" s="3">
-        <v>2.5341</v>
-      </c>
-      <c r="F35" s="3">
-        <v>2.5076000000000001</v>
-      </c>
-      <c r="G35" s="2">
-        <f t="shared" si="1"/>
-        <v>1.4299999999999979E-2</v>
+        <v>1.43E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>80</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="4">
+        <f t="shared" si="3"/>
+        <v>30.769230769230798</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.5312000000000001</v>
+      </c>
+      <c r="E36" s="5">
+        <v>2.5512999999999999</v>
+      </c>
+      <c r="F36" s="5">
+        <v>2.5184000000000002</v>
+      </c>
+      <c r="G36" s="4">
         <f t="shared" si="2"/>
-        <v>30.769230769230766</v>
-      </c>
-      <c r="D36" s="3">
-        <v>2.5312000000000001</v>
-      </c>
-      <c r="E36" s="3">
-        <v>2.5512999999999999</v>
-      </c>
-      <c r="F36" s="3">
-        <v>2.5184000000000002</v>
-      </c>
-      <c r="G36" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0099999999999785E-2</v>
+        <v>2.0099999999999799E-2</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>90</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="4">
+        <f t="shared" si="3"/>
+        <v>32.142857142857103</v>
+      </c>
+      <c r="D37" s="5">
+        <v>2.5402</v>
+      </c>
+      <c r="E37" s="5">
+        <v>2.5539999999999998</v>
+      </c>
+      <c r="F37" s="5">
+        <v>2.5297000000000001</v>
+      </c>
+      <c r="G37" s="4">
         <f t="shared" si="2"/>
-        <v>32.142857142857146</v>
-      </c>
-      <c r="D37" s="3">
-        <v>2.5402</v>
-      </c>
-      <c r="E37" s="3">
-        <v>2.5539999999999998</v>
-      </c>
-      <c r="F37" s="3">
-        <v>2.5297000000000001</v>
-      </c>
-      <c r="G37" s="2">
-        <f t="shared" si="1"/>
-        <v>1.3799999999999812E-2</v>
+        <v>1.37999999999998E-2</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>100</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="4">
+        <f t="shared" si="3"/>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2.5463</v>
+      </c>
+      <c r="E38" s="5">
+        <v>2.5655000000000001</v>
+      </c>
+      <c r="F38" s="5">
+        <v>2.5316000000000001</v>
+      </c>
+      <c r="G38" s="4">
         <f t="shared" si="2"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="D38" s="3">
-        <v>2.5463</v>
-      </c>
-      <c r="E38" s="3">
-        <v>2.5655000000000001</v>
-      </c>
-      <c r="F38" s="3">
-        <v>2.5316000000000001</v>
-      </c>
-      <c r="G38" s="2">
-        <f t="shared" si="1"/>
-        <v>1.9200000000000106E-2</v>
+        <v>1.9200000000000099E-2</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>110</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="4">
+        <f t="shared" si="3"/>
+        <v>34.375</v>
+      </c>
+      <c r="D39" s="5">
+        <v>2.5516000000000001</v>
+      </c>
+      <c r="E39" s="5">
+        <v>2.5701999999999998</v>
+      </c>
+      <c r="F39" s="5">
+        <v>2.5390000000000001</v>
+      </c>
+      <c r="G39" s="4">
         <f t="shared" si="2"/>
-        <v>34.375</v>
-      </c>
-      <c r="D39" s="3">
-        <v>2.5516000000000001</v>
-      </c>
-      <c r="E39" s="3">
-        <v>2.5701999999999998</v>
-      </c>
-      <c r="F39" s="3">
-        <v>2.5390000000000001</v>
-      </c>
-      <c r="G39" s="2">
-        <f t="shared" si="1"/>
-        <v>1.8599999999999728E-2</v>
+        <v>1.85999999999997E-2</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>120</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="4">
+        <f t="shared" si="3"/>
+        <v>35.294117647058798</v>
+      </c>
+      <c r="D40" s="5">
+        <v>2.5565000000000002</v>
+      </c>
+      <c r="E40" s="5">
+        <v>2.5743</v>
+      </c>
+      <c r="F40" s="5">
+        <v>2.5446</v>
+      </c>
+      <c r="G40" s="4">
         <f t="shared" si="2"/>
-        <v>35.294117647058819</v>
-      </c>
-      <c r="D40" s="3">
-        <v>2.5565000000000002</v>
-      </c>
-      <c r="E40" s="3">
-        <v>2.5743</v>
-      </c>
-      <c r="F40" s="3">
-        <v>2.5446</v>
-      </c>
-      <c r="G40" s="2">
-        <f t="shared" si="1"/>
-        <v>1.7799999999999816E-2</v>
+        <v>1.7799999999999799E-2</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>130</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="4">
+        <f t="shared" si="3"/>
+        <v>36.1111111111111</v>
+      </c>
+      <c r="D41" s="5">
+        <v>2.5600999999999998</v>
+      </c>
+      <c r="E41" s="5">
+        <v>2.5716000000000001</v>
+      </c>
+      <c r="F41" s="5">
+        <v>2.5488</v>
+      </c>
+      <c r="G41" s="4">
         <f t="shared" si="2"/>
-        <v>36.111111111111107</v>
-      </c>
-      <c r="D41" s="3">
-        <v>2.5600999999999998</v>
-      </c>
-      <c r="E41" s="3">
-        <v>2.5716000000000001</v>
-      </c>
-      <c r="F41" s="3">
-        <v>2.5488</v>
-      </c>
-      <c r="G41" s="2">
-        <f t="shared" si="1"/>
-        <v>1.1500000000000288E-2</v>
+        <v>1.15000000000003E-2</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>140</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="4">
+        <f t="shared" si="3"/>
+        <v>36.842105263157897</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2.5657999999999999</v>
+      </c>
+      <c r="E42" s="5">
+        <v>2.5832000000000002</v>
+      </c>
+      <c r="F42" s="5">
+        <v>2.5537000000000001</v>
+      </c>
+      <c r="G42" s="4">
         <f t="shared" si="2"/>
-        <v>36.842105263157897</v>
-      </c>
-      <c r="D42" s="3">
-        <v>2.5657999999999999</v>
-      </c>
-      <c r="E42" s="3">
-        <v>2.5832000000000002</v>
-      </c>
-      <c r="F42" s="3">
-        <v>2.5537000000000001</v>
-      </c>
-      <c r="G42" s="2">
-        <f t="shared" si="1"/>
-        <v>1.7400000000000304E-2</v>
+        <v>1.7400000000000301E-2</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>150</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="4">
+        <f t="shared" si="3"/>
+        <v>37.5</v>
+      </c>
+      <c r="D43" s="5">
+        <v>2.5674000000000001</v>
+      </c>
+      <c r="E43" s="5">
+        <v>2.5868000000000002</v>
+      </c>
+      <c r="F43" s="5">
+        <v>2.5537000000000001</v>
+      </c>
+      <c r="G43" s="4">
         <f t="shared" si="2"/>
-        <v>37.5</v>
-      </c>
-      <c r="D43" s="3">
-        <v>2.5674000000000001</v>
-      </c>
-      <c r="E43" s="3">
-        <v>2.5868000000000002</v>
-      </c>
-      <c r="F43" s="3">
-        <v>2.5537000000000001</v>
-      </c>
-      <c r="G43" s="2">
-        <f t="shared" si="1"/>
-        <v>1.9400000000000084E-2</v>
+        <v>1.9400000000000101E-2</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>160</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="4">
+        <f t="shared" si="3"/>
+        <v>38.095238095238102</v>
+      </c>
+      <c r="D44" s="5">
+        <v>2.5714999999999999</v>
+      </c>
+      <c r="E44" s="5">
+        <v>2.5846</v>
+      </c>
+      <c r="F44" s="5">
+        <v>2.5596000000000001</v>
+      </c>
+      <c r="G44" s="4">
         <f t="shared" si="2"/>
-        <v>38.095238095238095</v>
-      </c>
-      <c r="D44" s="3">
-        <v>2.5714999999999999</v>
-      </c>
-      <c r="E44" s="3">
-        <v>2.5846</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2.5596000000000001</v>
-      </c>
-      <c r="G44" s="2">
-        <f t="shared" si="1"/>
-        <v>1.3100000000000112E-2</v>
+        <v>1.3100000000000099E-2</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>170</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="4">
+        <f t="shared" si="3"/>
+        <v>38.636363636363598</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2.5728</v>
+      </c>
+      <c r="E45" s="5">
+        <v>2.59</v>
+      </c>
+      <c r="F45" s="5">
+        <v>2.5615999999999999</v>
+      </c>
+      <c r="G45" s="4">
         <f t="shared" si="2"/>
-        <v>38.636363636363633</v>
-      </c>
-      <c r="D45" s="3">
-        <v>2.5728</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2.59</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2.5615999999999999</v>
-      </c>
-      <c r="G45" s="2">
-        <f t="shared" si="1"/>
-        <v>1.7199999999999882E-2</v>
+        <v>1.7199999999999899E-2</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>180</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="4">
+        <f t="shared" si="3"/>
+        <v>39.130434782608702</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="4">
         <f t="shared" si="2"/>
-        <v>39.130434782608695</v>
-      </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="2">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4591,15 +5772,15 @@
       <c r="B47">
         <v>190</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="4">
+        <f t="shared" si="3"/>
+        <v>39.5833333333333</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="4">
         <f t="shared" si="2"/>
-        <v>39.583333333333336</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="2">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4607,22 +5788,22 @@
       <c r="B48">
         <v>200</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="4">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="4">
         <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="2">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="G51" s="2">
+      <c r="G51" s="4">
         <f>AVERAGE(G53:G73)</f>
-        <v>2.2504761904761944E-2</v>
+        <v>2.2504761904761899E-2</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="17" x14ac:dyDescent="0.2">
@@ -4639,25 +5820,25 @@
       <c r="F52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>5</v>
+      <c r="G52" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>0</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="4">
         <v>2.0516999999999999</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="4">
         <v>2.0722999999999998</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="4">
         <v>1.9874000000000001</v>
       </c>
-      <c r="G53" s="2">
-        <f t="shared" ref="G53:G74" si="3">MAX((E53-D53),(D53-F53))</f>
+      <c r="G53" s="4">
+        <f t="shared" ref="G53:G74" si="4">MAX((E53-D53),(D53-F53))</f>
         <v>6.4299999999999802E-2</v>
       </c>
     </row>
@@ -4665,154 +5846,154 @@
       <c r="B54">
         <v>10</v>
       </c>
-      <c r="C54" s="2">
-        <f>1/((1/C$1)+(1/$B54))</f>
-        <v>9.0909090909090917</v>
-      </c>
-      <c r="D54" s="2">
+      <c r="C54" s="4">
+        <f t="shared" ref="C54:C73" si="5">1/((1/C$1)+(1/$B54))</f>
+        <v>9.0909090909090899</v>
+      </c>
+      <c r="D54" s="4">
         <v>2.3736000000000002</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="4">
         <v>2.3942000000000001</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="4">
         <v>2.3578999999999999</v>
       </c>
-      <c r="G54" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0599999999999952E-2</v>
+      <c r="G54" s="4">
+        <f t="shared" si="4"/>
+        <v>2.06E-2</v>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>20</v>
       </c>
-      <c r="C55" s="2">
-        <f>1/((1/C$1)+(1/$B55))</f>
-        <v>16.666666666666664</v>
-      </c>
-      <c r="D55" s="2">
+      <c r="C55" s="4">
+        <f t="shared" si="5"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="D55" s="4">
         <v>2.5124</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="4">
         <v>2.5324</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="4">
         <v>2.4967999999999999</v>
       </c>
-      <c r="G55" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0000000000000018E-2</v>
+      <c r="G55" s="4">
+        <f t="shared" si="4"/>
+        <v>0.02</v>
       </c>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B56">
         <v>30</v>
       </c>
-      <c r="C56" s="2">
-        <f>1/((1/C$1)+(1/$B56))</f>
-        <v>23.076923076923077</v>
-      </c>
-      <c r="D56" s="2">
+      <c r="C56" s="4">
+        <f t="shared" si="5"/>
+        <v>23.076923076923102</v>
+      </c>
+      <c r="D56" s="4">
         <v>2.5869</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="4">
         <v>2.6074999999999999</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="4">
         <v>2.5731000000000002</v>
       </c>
-      <c r="G56" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0599999999999952E-2</v>
+      <c r="G56" s="4">
+        <f t="shared" si="4"/>
+        <v>2.06E-2</v>
       </c>
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>40</v>
       </c>
-      <c r="C57" s="2">
-        <f>1/((1/C$1)+(1/$B57))</f>
-        <v>28.571428571428569</v>
-      </c>
-      <c r="D57" s="2">
+      <c r="C57" s="4">
+        <f t="shared" si="5"/>
+        <v>28.571428571428601</v>
+      </c>
+      <c r="D57" s="4">
         <v>2.6324999999999998</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="4">
         <v>2.6636000000000002</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="4">
         <v>2.6187</v>
       </c>
-      <c r="G57" s="2">
-        <f t="shared" si="3"/>
-        <v>3.110000000000035E-2</v>
+      <c r="G57" s="4">
+        <f t="shared" si="4"/>
+        <v>3.1100000000000301E-2</v>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>50</v>
       </c>
-      <c r="C58" s="2">
-        <f>1/((1/C$1)+(1/$B58))</f>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="D58" s="2">
+      <c r="C58" s="4">
+        <f t="shared" si="5"/>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D58" s="4">
         <v>2.6621000000000001</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="4">
         <v>2.6829999999999998</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="4">
         <v>2.6488999999999998</v>
       </c>
-      <c r="G58" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0899999999999697E-2</v>
+      <c r="G58" s="4">
+        <f t="shared" si="4"/>
+        <v>2.08999999999997E-2</v>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>60</v>
       </c>
-      <c r="C59" s="2">
-        <f>1/((1/C$1)+(1/$B59))</f>
+      <c r="C59" s="4">
+        <f t="shared" si="5"/>
         <v>37.5</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="4">
         <v>2.6844999999999999</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="4">
         <v>2.7017000000000002</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="4">
         <v>2.6737000000000002</v>
       </c>
-      <c r="G59" s="2">
-        <f t="shared" si="3"/>
-        <v>1.7200000000000326E-2</v>
+      <c r="G59" s="4">
+        <f t="shared" si="4"/>
+        <v>1.7200000000000298E-2</v>
       </c>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>70</v>
       </c>
-      <c r="C60" s="2">
-        <f>1/((1/C$1)+(1/$B60))</f>
+      <c r="C60" s="4">
+        <f t="shared" si="5"/>
         <v>41.176470588235297</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="4">
         <v>2.6987000000000001</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="4">
         <v>2.7216</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="4">
         <v>2.6833</v>
       </c>
-      <c r="G60" s="2">
-        <f t="shared" si="3"/>
-        <v>2.289999999999992E-2</v>
+      <c r="G60" s="4">
+        <f t="shared" si="4"/>
+        <v>2.28999999999999E-2</v>
       </c>
       <c r="M60">
         <v>2.5411999999999999</v>
@@ -4822,33 +6003,33 @@
       </c>
       <c r="O60">
         <f>N60-M60</f>
-        <v>6.1300000000000132E-2</v>
-      </c>
-      <c r="P60" s="6">
+        <v>6.1300000000000097E-2</v>
+      </c>
+      <c r="P60" s="7">
         <f>D63-D58</f>
-        <v>6.109999999999971E-2</v>
+        <v>6.1099999999999703E-2</v>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>80</v>
       </c>
-      <c r="C61" s="2">
-        <f>1/((1/C$1)+(1/$B61))</f>
-        <v>44.444444444444443</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="C61" s="4">
+        <f t="shared" si="5"/>
+        <v>44.4444444444444</v>
+      </c>
+      <c r="D61" s="4">
         <v>2.7098</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="4">
         <v>2.7311000000000001</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="4">
         <v>2.6945999999999999</v>
       </c>
-      <c r="G61" s="2">
-        <f t="shared" si="3"/>
-        <v>2.1300000000000097E-2</v>
+      <c r="G61" s="4">
+        <f t="shared" si="4"/>
+        <v>2.13000000000001E-2</v>
       </c>
       <c r="M61">
         <v>1.2826</v>
@@ -4858,289 +6039,289 @@
       </c>
       <c r="O61">
         <f>N61-M61</f>
-        <v>5.6799999999999962E-2</v>
+        <v>5.6800000000000003E-2</v>
       </c>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>90</v>
       </c>
-      <c r="C62" s="2">
-        <f>1/((1/C$1)+(1/$B62))</f>
-        <v>47.368421052631575</v>
-      </c>
-      <c r="D62" s="2">
+      <c r="C62" s="4">
+        <f t="shared" si="5"/>
+        <v>47.368421052631597</v>
+      </c>
+      <c r="D62" s="4">
         <v>2.7170000000000001</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="4">
         <v>2.7402000000000002</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="4">
         <v>2.7014</v>
       </c>
-      <c r="G62" s="2">
-        <f t="shared" si="3"/>
-        <v>2.3200000000000109E-2</v>
+      <c r="G62" s="4">
+        <f t="shared" si="4"/>
+        <v>2.3200000000000099E-2</v>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B63">
         <v>100</v>
       </c>
-      <c r="C63" s="2">
-        <f>1/((1/C$1)+(1/$B63))</f>
+      <c r="C63" s="4">
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="4">
         <v>2.7231999999999998</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="4">
         <v>2.7450999999999999</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="4">
         <v>2.7088000000000001</v>
       </c>
-      <c r="G63" s="2">
-        <f t="shared" si="3"/>
-        <v>2.1900000000000031E-2</v>
+      <c r="G63" s="4">
+        <f t="shared" si="4"/>
+        <v>2.1899999999999999E-2</v>
       </c>
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>110</v>
       </c>
-      <c r="C64" s="2">
-        <f>1/((1/C$1)+(1/$B64))</f>
-        <v>52.380952380952387</v>
-      </c>
-      <c r="D64" s="2">
+      <c r="C64" s="4">
+        <f t="shared" si="5"/>
+        <v>52.380952380952401</v>
+      </c>
+      <c r="D64" s="4">
         <v>2.7288999999999999</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="4">
         <v>2.7507999999999999</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="4">
         <v>2.7149999999999999</v>
       </c>
-      <c r="G64" s="2">
-        <f t="shared" si="3"/>
-        <v>2.1900000000000031E-2</v>
+      <c r="G64" s="4">
+        <f t="shared" si="4"/>
+        <v>2.1899999999999999E-2</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>120</v>
       </c>
-      <c r="C65" s="2">
-        <f>1/((1/C$1)+(1/$B65))</f>
-        <v>54.545454545454547</v>
-      </c>
-      <c r="D65" s="2">
+      <c r="C65" s="4">
+        <f t="shared" si="5"/>
+        <v>54.545454545454497</v>
+      </c>
+      <c r="D65" s="4">
         <v>2.7328000000000001</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="4">
         <v>2.7524999999999999</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="4">
         <v>2.7195999999999998</v>
       </c>
-      <c r="G65" s="2">
-        <f>MAX((E65-D65),(D65-F65))</f>
-        <v>1.9699999999999829E-2</v>
+      <c r="G65" s="4">
+        <f t="shared" si="4"/>
+        <v>1.9699999999999801E-2</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>130</v>
       </c>
-      <c r="C66" s="2">
-        <f>1/((1/C$1)+(1/$B66))</f>
-        <v>56.521739130434774</v>
-      </c>
-      <c r="D66" s="2">
+      <c r="C66" s="4">
+        <f t="shared" si="5"/>
+        <v>56.521739130434803</v>
+      </c>
+      <c r="D66" s="4">
         <v>2.7357999999999998</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="4">
         <v>2.7542</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="4">
         <v>2.7221000000000002</v>
       </c>
-      <c r="G66" s="2">
-        <f>MAX((E66-D66),(D66-F66))</f>
-        <v>1.8400000000000194E-2</v>
+      <c r="G66" s="4">
+        <f t="shared" si="4"/>
+        <v>1.8400000000000201E-2</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>140</v>
       </c>
-      <c r="C67" s="2">
-        <f>1/((1/C$1)+(1/$B67))</f>
-        <v>58.333333333333329</v>
-      </c>
-      <c r="D67" s="2">
+      <c r="C67" s="4">
+        <f t="shared" si="5"/>
+        <v>58.3333333333333</v>
+      </c>
+      <c r="D67" s="4">
         <v>2.7385000000000002</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="4">
         <v>2.7557</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="4">
         <v>2.7265000000000001</v>
       </c>
-      <c r="G67" s="2">
-        <f t="shared" si="3"/>
-        <v>1.7199999999999882E-2</v>
+      <c r="G67" s="4">
+        <f t="shared" si="4"/>
+        <v>1.7199999999999899E-2</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>150</v>
       </c>
-      <c r="C68" s="2">
-        <f>1/((1/C$1)+(1/$B68))</f>
+      <c r="C68" s="4">
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="4">
         <v>2.7406999999999999</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="4">
         <v>2.7608000000000001</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="4">
         <v>2.7277</v>
       </c>
-      <c r="G68" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0100000000000229E-2</v>
+      <c r="G68" s="4">
+        <f t="shared" si="4"/>
+        <v>2.0100000000000201E-2</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>160</v>
       </c>
-      <c r="C69" s="2">
-        <f>1/((1/C$1)+(1/$B69))</f>
-        <v>61.538461538461533</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="C69" s="4">
+        <f t="shared" si="5"/>
+        <v>61.538461538461497</v>
+      </c>
+      <c r="D69" s="4">
         <v>2.7435999999999998</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="4">
         <v>2.7627999999999999</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="4">
         <v>2.7302</v>
       </c>
-      <c r="G69" s="2">
-        <f t="shared" si="3"/>
-        <v>1.9200000000000106E-2</v>
+      <c r="G69" s="4">
+        <f t="shared" si="4"/>
+        <v>1.9200000000000099E-2</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B70">
         <v>170</v>
       </c>
-      <c r="C70" s="2">
-        <f>1/((1/C$1)+(1/$B70))</f>
-        <v>62.962962962962955</v>
-      </c>
-      <c r="D70" s="2">
+      <c r="C70" s="4">
+        <f t="shared" si="5"/>
+        <v>62.962962962962997</v>
+      </c>
+      <c r="D70" s="4">
         <v>2.7444999999999999</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="4">
         <v>2.7616000000000001</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="4">
         <v>2.7277</v>
       </c>
-      <c r="G70" s="2">
-        <f t="shared" si="3"/>
-        <v>1.7100000000000115E-2</v>
+      <c r="G70" s="4">
+        <f t="shared" si="4"/>
+        <v>1.7100000000000101E-2</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>180</v>
       </c>
-      <c r="C71" s="2">
-        <f>1/((1/C$1)+(1/$B71))</f>
-        <v>64.285714285714292</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="C71" s="4">
+        <f t="shared" si="5"/>
+        <v>64.285714285714306</v>
+      </c>
+      <c r="D71" s="4">
         <v>2.7448999999999999</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="4">
         <v>2.7612999999999999</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="4">
         <v>2.7303999999999999</v>
       </c>
-      <c r="G71" s="2">
-        <f t="shared" si="3"/>
-        <v>1.639999999999997E-2</v>
+      <c r="G71" s="4">
+        <f t="shared" si="4"/>
+        <v>1.6400000000000001E-2</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>190</v>
       </c>
-      <c r="C72" s="2">
-        <f>1/((1/C$1)+(1/$B72))</f>
-        <v>65.517241379310335</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="C72" s="4">
+        <f t="shared" si="5"/>
+        <v>65.517241379310306</v>
+      </c>
+      <c r="D72" s="4">
         <v>2.7464</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="4">
         <v>2.7643</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="4">
         <v>2.7330999999999999</v>
       </c>
-      <c r="G72" s="2">
-        <f t="shared" si="3"/>
-        <v>1.7900000000000027E-2</v>
+      <c r="G72" s="4">
+        <f t="shared" si="4"/>
+        <v>1.7899999999999999E-2</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>200</v>
       </c>
-      <c r="C73" s="2">
-        <f>1/((1/C$1)+(1/$B73))</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="D73" s="2">
+      <c r="C73" s="4">
+        <f t="shared" si="5"/>
+        <v>66.6666666666667</v>
+      </c>
+      <c r="D73" s="4">
         <v>2.7477</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="4">
         <v>2.7684000000000002</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="4">
         <v>2.7338</v>
       </c>
-      <c r="G73" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0700000000000163E-2</v>
+      <c r="G73" s="4">
+        <f t="shared" si="4"/>
+        <v>2.0700000000000201E-2</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="4">
         <v>2.7704</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="4">
         <v>2.7915000000000001</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="4">
         <v>2.7536999999999998</v>
       </c>
-      <c r="G74" s="2">
-        <f t="shared" si="3"/>
-        <v>2.1100000000000119E-2</v>
+      <c r="G74" s="4">
+        <f t="shared" si="4"/>
+        <v>2.1100000000000101E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5150,11 +6331,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E196836-4278-7A49-BC8B-0456AD13A52F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5162,9 +6343,9 @@
       <c r="C1" s="1">
         <v>100</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="4">
         <f>AVERAGE(G3:G23)</f>
-        <v>2.038385714285714</v>
+        <v>2.03838571428571</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="17" x14ac:dyDescent="0.2">
@@ -5181,502 +6362,502 @@
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>0</v>
       </c>
-      <c r="D3" s="2">
-        <v>3.3399999999999874E-2</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="4">
+        <v>3.3399999999999902E-2</v>
+      </c>
+      <c r="E3" s="4">
         <v>2.0722999999999998</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>1.9874000000000001</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G23" si="0">MAX((E3-D3),(D3-F3))</f>
         <v>2.0388999999999999</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>10</v>
       </c>
-      <c r="C4" s="2">
-        <f>1/((1/C$1)+(1/$B4))</f>
-        <v>9.0909090909090917</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="4">
+        <f t="shared" ref="C4:C23" si="1">1/((1/C$1)+(1/$B4))</f>
+        <v>9.0909090909090899</v>
+      </c>
+      <c r="D4" s="4">
         <v>0.30659999999999998</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="4">
         <v>2.3422999999999998</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>2.2652000000000001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="4">
         <f t="shared" si="0"/>
         <v>2.0356999999999998</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>20</v>
       </c>
-      <c r="C5" s="2">
-        <f>1/((1/C$1)+(1/$B5))</f>
-        <v>16.666666666666664</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.43270000000000008</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="C5" s="4">
+        <f t="shared" si="1"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.43269999999999997</v>
+      </c>
+      <c r="E5" s="4">
         <v>2.4666999999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>2.3839999999999999</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="4">
         <f t="shared" si="0"/>
         <v>2.0339999999999998</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>30</v>
       </c>
-      <c r="C6" s="2">
-        <f>1/((1/C$1)+(1/$B6))</f>
-        <v>23.076923076923077</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6" s="4">
+        <f t="shared" si="1"/>
+        <v>23.076923076923102</v>
+      </c>
+      <c r="D6" s="4">
         <v>0.50170000000000003</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="4">
         <v>2.5400999999999998</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>2.4559000000000002</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>2.0383999999999998</v>
-      </c>
-      <c r="H6" s="3"/>
+        <v>2.0384000000000002</v>
+      </c>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>40</v>
       </c>
-      <c r="C7" s="2">
-        <f>1/((1/C$1)+(1/$B7))</f>
-        <v>28.571428571428569</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.54280000000000017</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="C7" s="4">
+        <f t="shared" si="1"/>
+        <v>28.571428571428601</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.54279999999999995</v>
+      </c>
+      <c r="E7" s="4">
         <v>2.5808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>2.5032999999999999</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="4">
         <f t="shared" si="0"/>
         <v>2.0379999999999998</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>50</v>
       </c>
-      <c r="C8" s="2">
-        <f>1/((1/C$1)+(1/$B8))</f>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.57189999999999985</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="C8" s="4">
+        <f t="shared" si="1"/>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.57189999999999996</v>
+      </c>
+      <c r="E8" s="4">
         <v>2.6071</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>2.5303</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="4">
         <f t="shared" si="0"/>
         <v>2.0352000000000001</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>60</v>
       </c>
-      <c r="C9" s="2">
-        <f>1/((1/C$1)+(1/$B9))</f>
+      <c r="C9" s="4">
+        <f t="shared" si="1"/>
         <v>37.5</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="4">
         <v>0.59089999999999998</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="4">
         <v>2.625</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>2.5497000000000001</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="4">
         <f t="shared" si="0"/>
         <v>2.0341</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>70</v>
       </c>
-      <c r="C10" s="2">
-        <f>1/((1/C$1)+(1/$B10))</f>
+      <c r="C10" s="4">
+        <f t="shared" si="1"/>
         <v>41.176470588235297</v>
       </c>
-      <c r="D10" s="2">
-        <v>0.60490000000000022</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D10" s="4">
+        <v>0.60489999999999999</v>
+      </c>
+      <c r="E10" s="4">
         <v>2.6427</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>2.5653999999999999</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="4">
         <f t="shared" si="0"/>
         <v>2.0377999999999998</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>80</v>
       </c>
-      <c r="C11" s="2">
-        <f>1/((1/C$1)+(1/$B11))</f>
-        <v>44.444444444444443</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="C11" s="4">
+        <f t="shared" si="1"/>
+        <v>44.4444444444444</v>
+      </c>
+      <c r="D11" s="4">
         <v>0.61660000000000004</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="4">
         <v>2.6526999999999998</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>2.5720000000000001</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="4">
         <f t="shared" si="0"/>
         <v>2.0360999999999998</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>90</v>
       </c>
-      <c r="C12" s="2">
-        <f>1/((1/C$1)+(1/$B12))</f>
-        <v>47.368421052631575</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.62579999999999991</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="C12" s="4">
+        <f t="shared" si="1"/>
+        <v>47.368421052631597</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.62580000000000002</v>
+      </c>
+      <c r="E12" s="4">
         <v>2.6608000000000001</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>2.5859999999999999</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="4">
         <f t="shared" si="0"/>
         <v>2.0350000000000001</v>
       </c>
-      <c r="H12" s="3"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>100</v>
       </c>
-      <c r="C13" s="2">
-        <f>1/((1/C$1)+(1/$B13))</f>
+      <c r="C13" s="4">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="D13" s="2">
-        <v>0.63379999999999992</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="D13" s="4">
+        <v>0.63380000000000003</v>
+      </c>
+      <c r="E13" s="4">
         <v>2.6709000000000001</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>2.5897000000000001</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="4">
         <f t="shared" si="0"/>
         <v>2.0371000000000001</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>110</v>
       </c>
-      <c r="C14" s="2">
-        <f>1/((1/C$1)+(1/$B14))</f>
-        <v>52.380952380952387</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.64029999999999987</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="C14" s="4">
+        <f t="shared" si="1"/>
+        <v>52.380952380952401</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.64029999999999998</v>
+      </c>
+      <c r="E14" s="4">
         <v>2.6791999999999998</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>2.6013999999999999</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="4">
         <f t="shared" si="0"/>
         <v>2.0388999999999999</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>120</v>
       </c>
-      <c r="C15" s="2">
-        <f>1/((1/C$1)+(1/$B15))</f>
-        <v>54.545454545454547</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="C15" s="4">
+        <f t="shared" si="1"/>
+        <v>54.545454545454497</v>
+      </c>
+      <c r="D15" s="4">
         <v>0.64559999999999995</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="4">
         <v>2.6854</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>2.6019000000000001</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="4">
         <f t="shared" si="0"/>
         <v>2.0398000000000001</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>130</v>
       </c>
-      <c r="C16" s="2">
-        <f>1/((1/C$1)+(1/$B16))</f>
-        <v>56.521739130434774</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.6503000000000001</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="C16" s="4">
+        <f t="shared" si="1"/>
+        <v>56.521739130434803</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.65029999999999999</v>
+      </c>
+      <c r="E16" s="4">
         <v>2.6924999999999999</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>2.6996000000000002</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="4">
         <f t="shared" si="0"/>
         <v>2.0421999999999998</v>
       </c>
-      <c r="H16" s="3"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>140</v>
       </c>
-      <c r="C17" s="2">
-        <f>1/((1/C$1)+(1/$B17))</f>
-        <v>58.333333333333329</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.65450000000000008</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="C17" s="4">
+        <f t="shared" si="1"/>
+        <v>58.3333333333333</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.65449999999999997</v>
+      </c>
+      <c r="E17" s="4">
         <v>2.6926999999999999</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="4">
         <v>2.6105</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="4">
         <f t="shared" si="0"/>
         <v>2.0381999999999998</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>150</v>
       </c>
-      <c r="C18" s="2">
-        <f>1/((1/C$1)+(1/$B18))</f>
+      <c r="C18" s="4">
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="D18" s="2">
-        <v>0.6581999999999999</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="D18" s="4">
+        <v>0.65820000000000001</v>
+      </c>
+      <c r="E18" s="4">
         <v>2.6959</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>2.6189</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="4">
         <f t="shared" si="0"/>
         <v>2.0377000000000001</v>
       </c>
-      <c r="H18" s="3"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>160</v>
       </c>
-      <c r="C19" s="2">
-        <f>1/((1/C$1)+(1/$B19))</f>
-        <v>61.538461538461533</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.66089999999999982</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="C19" s="4">
+        <f t="shared" si="1"/>
+        <v>61.538461538461497</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.66090000000000004</v>
+      </c>
+      <c r="E19" s="4">
         <v>2.7042999999999999</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="4">
         <v>2.6183999999999998</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="4">
         <f t="shared" si="0"/>
         <v>2.0434000000000001</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>170</v>
       </c>
-      <c r="C20" s="2">
-        <f>1/((1/C$1)+(1/$B20))</f>
-        <v>62.962962962962955</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C20" s="4">
+        <f t="shared" si="1"/>
+        <v>62.962962962962997</v>
+      </c>
+      <c r="D20" s="4">
         <v>0.6633</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="4">
         <v>2.6991000000000001</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="4">
         <v>2.6141999999999999</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="4">
         <f t="shared" si="0"/>
         <v>2.0358000000000001</v>
       </c>
-      <c r="H20" s="3"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>180</v>
       </c>
-      <c r="C21" s="2">
-        <f>1/((1/C$1)+(1/$B21))</f>
-        <v>64.285714285714292</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.6655000000000002</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="C21" s="4">
+        <f t="shared" si="1"/>
+        <v>64.285714285714306</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.66549999999999998</v>
+      </c>
+      <c r="E21" s="4">
         <v>2.7054999999999998</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>2.6189</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="4">
         <f t="shared" si="0"/>
-        <v>2.0399999999999996</v>
-      </c>
-      <c r="H21" s="3"/>
+        <v>2.04</v>
+      </c>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>190</v>
       </c>
-      <c r="C22" s="2">
-        <f>1/((1/C$1)+(1/$B22))</f>
-        <v>65.517241379310335</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.66820000000000013</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="C22" s="4">
+        <f t="shared" si="1"/>
+        <v>65.517241379310306</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.66820000000000002</v>
+      </c>
+      <c r="E22" s="4">
         <v>2.7080000000000002</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4">
         <v>2.6208</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="4">
         <f t="shared" si="0"/>
         <v>2.0398000000000001</v>
       </c>
-      <c r="H22" s="3"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>200</v>
       </c>
-      <c r="C23" s="2">
-        <f>1/((1/C$1)+(1/$B23))</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.67019999999999991</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="C23" s="4">
+        <f t="shared" si="1"/>
+        <v>66.6666666666667</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="E23" s="4">
         <v>2.7202000000000002</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="4">
         <v>2.6316000000000002</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="4">
         <f t="shared" si="0"/>
-        <v>2.0500000000000003</v>
-      </c>
-      <c r="H23" s="3"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="H23" s="5"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G25" s="2"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C26" s="1">
         <v>50</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="4">
         <f>AVERAGE(G28:G45)</f>
-        <v>2.0159888888888893</v>
+        <v>2.0159888888888902</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="17" x14ac:dyDescent="0.2">
@@ -5692,479 +6873,479 @@
       <c r="F27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>0</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="3">
-        <v>8.7000000000001521E-3</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="C28" s="4"/>
+      <c r="D28" s="5">
+        <v>8.7000000000001503E-3</v>
+      </c>
+      <c r="E28" s="5">
         <v>2.0209000000000001</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="5">
         <v>1.9922</v>
       </c>
-      <c r="G28" s="2">
-        <f t="shared" ref="G28:G48" si="1">MAX((E28-D28),(D28-F28))</f>
+      <c r="G28" s="4">
+        <f t="shared" ref="G28:G48" si="2">MAX((E28-D28),(D28-F28))</f>
         <v>2.0122</v>
       </c>
-      <c r="H28" s="3"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>10</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="4">
         <f>1/((1/C$26)+(1/$B29))</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="D29" s="3">
-        <v>0.25760000000000005</v>
-      </c>
-      <c r="E29" s="3">
+        <v>8.3333333333333304</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0.2576</v>
+      </c>
+      <c r="E29" s="5">
         <v>2.2719999999999998</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="5">
         <v>2.2450000000000001</v>
       </c>
-      <c r="G29" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0143999999999997</v>
-      </c>
-      <c r="H29" s="3"/>
+      <c r="G29" s="4">
+        <f t="shared" si="2"/>
+        <v>2.0144000000000002</v>
+      </c>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>20</v>
       </c>
-      <c r="C30" s="2">
-        <f t="shared" ref="C30:C48" si="2">1/((1/C$26)+(1/$B30))</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="D30" s="3">
-        <v>0.37020000000000008</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="C30" s="4">
+        <f t="shared" ref="C30:C48" si="3">1/((1/C$26)+(1/$B30))</f>
+        <v>14.285714285714301</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0.37019999999999997</v>
+      </c>
+      <c r="E30" s="5">
         <v>2.3845999999999998</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="5">
         <v>2.3591000000000002</v>
       </c>
-      <c r="G30" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0143999999999997</v>
-      </c>
-      <c r="H30" s="3"/>
+      <c r="G30" s="4">
+        <f t="shared" si="2"/>
+        <v>2.0144000000000002</v>
+      </c>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>30</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="4">
+        <f t="shared" si="3"/>
+        <v>18.75</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0.42630000000000001</v>
+      </c>
+      <c r="E31" s="5">
+        <v>2.4418000000000002</v>
+      </c>
+      <c r="F31" s="5">
+        <v>2.4131999999999998</v>
+      </c>
+      <c r="G31" s="4">
         <f t="shared" si="2"/>
-        <v>18.75</v>
-      </c>
-      <c r="D31" s="3">
-        <v>0.4262999999999999</v>
-      </c>
-      <c r="E31" s="3">
-        <v>2.4418000000000002</v>
-      </c>
-      <c r="F31" s="3">
-        <v>2.4131999999999998</v>
-      </c>
-      <c r="G31" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0155000000000003</v>
-      </c>
-      <c r="H31" s="3"/>
+        <v>2.0154999999999998</v>
+      </c>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>40</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="4">
+        <f t="shared" si="3"/>
+        <v>22.2222222222222</v>
+      </c>
+      <c r="D32" s="5">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2.4851999999999999</v>
+      </c>
+      <c r="F32" s="5">
+        <v>2.4519000000000002</v>
+      </c>
+      <c r="G32" s="4">
         <f t="shared" si="2"/>
-        <v>22.222222222222221</v>
-      </c>
-      <c r="D32" s="3">
-        <v>0.46499999999999986</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2.4851999999999999</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2.4519000000000002</v>
-      </c>
-      <c r="G32" s="2">
-        <f t="shared" si="1"/>
         <v>2.0202</v>
       </c>
-      <c r="H32" s="3"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>50</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="4">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="D33" s="5">
+        <v>0.4889</v>
+      </c>
+      <c r="E33" s="5">
+        <v>2.5017</v>
+      </c>
+      <c r="F33" s="5">
+        <v>2.4763999999999999</v>
+      </c>
+      <c r="G33" s="4">
         <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-      <c r="D33" s="3">
-        <v>0.48890000000000011</v>
-      </c>
-      <c r="E33" s="3">
-        <v>2.5017</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2.4763999999999999</v>
-      </c>
-      <c r="G33" s="2">
-        <f t="shared" si="1"/>
         <v>2.0127999999999999</v>
       </c>
-      <c r="H33" s="3"/>
+      <c r="H33" s="5"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>60</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="4">
+        <f t="shared" si="3"/>
+        <v>27.272727272727298</v>
+      </c>
+      <c r="D34" s="5">
+        <v>0.50590000000000002</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2.5217999999999998</v>
+      </c>
+      <c r="F34" s="5">
+        <v>2.4921000000000002</v>
+      </c>
+      <c r="G34" s="4">
         <f t="shared" si="2"/>
-        <v>27.272727272727273</v>
-      </c>
-      <c r="D34" s="3">
-        <v>0.50590000000000002</v>
-      </c>
-      <c r="E34" s="3">
-        <v>2.5217999999999998</v>
-      </c>
-      <c r="F34" s="3">
-        <v>2.4921000000000002</v>
-      </c>
-      <c r="G34" s="2">
-        <f t="shared" si="1"/>
         <v>2.0158999999999998</v>
       </c>
-      <c r="H34" s="3"/>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>70</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="4">
+        <f t="shared" si="3"/>
+        <v>29.1666666666667</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0.51980000000000004</v>
+      </c>
+      <c r="E35" s="5">
+        <v>2.5341</v>
+      </c>
+      <c r="F35" s="5">
+        <v>2.5076000000000001</v>
+      </c>
+      <c r="G35" s="4">
         <f t="shared" si="2"/>
-        <v>29.166666666666664</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0.51980000000000004</v>
-      </c>
-      <c r="E35" s="3">
-        <v>2.5341</v>
-      </c>
-      <c r="F35" s="3">
-        <v>2.5076000000000001</v>
-      </c>
-      <c r="G35" s="2">
-        <f t="shared" si="1"/>
         <v>2.0143</v>
       </c>
-      <c r="H35" s="3"/>
+      <c r="H35" s="5"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>80</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="4">
+        <f t="shared" si="3"/>
+        <v>30.769230769230798</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="E36" s="5">
+        <v>2.5512999999999999</v>
+      </c>
+      <c r="F36" s="5">
+        <v>2.5184000000000002</v>
+      </c>
+      <c r="G36" s="4">
         <f t="shared" si="2"/>
-        <v>30.769230769230766</v>
-      </c>
-      <c r="D36" s="3">
-        <v>0.53120000000000012</v>
-      </c>
-      <c r="E36" s="3">
-        <v>2.5512999999999999</v>
-      </c>
-      <c r="F36" s="3">
-        <v>2.5184000000000002</v>
-      </c>
-      <c r="G36" s="2">
-        <f t="shared" si="1"/>
         <v>2.0200999999999998</v>
       </c>
-      <c r="H36" s="3"/>
+      <c r="H36" s="5"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>90</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="4">
+        <f t="shared" si="3"/>
+        <v>32.142857142857103</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0.54020000000000001</v>
+      </c>
+      <c r="E37" s="5">
+        <v>2.5539999999999998</v>
+      </c>
+      <c r="F37" s="5">
+        <v>2.5297000000000001</v>
+      </c>
+      <c r="G37" s="4">
         <f t="shared" si="2"/>
-        <v>32.142857142857146</v>
-      </c>
-      <c r="D37" s="3">
-        <v>0.54020000000000001</v>
-      </c>
-      <c r="E37" s="3">
-        <v>2.5539999999999998</v>
-      </c>
-      <c r="F37" s="3">
-        <v>2.5297000000000001</v>
-      </c>
-      <c r="G37" s="2">
-        <f t="shared" si="1"/>
         <v>2.0137999999999998</v>
       </c>
-      <c r="H37" s="3"/>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>100</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="4">
+        <f t="shared" si="3"/>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D38" s="5">
+        <v>0.54630000000000001</v>
+      </c>
+      <c r="E38" s="5">
+        <v>2.5655000000000001</v>
+      </c>
+      <c r="F38" s="5">
+        <v>2.5316000000000001</v>
+      </c>
+      <c r="G38" s="4">
         <f t="shared" si="2"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="D38" s="3">
-        <v>0.54630000000000001</v>
-      </c>
-      <c r="E38" s="3">
-        <v>2.5655000000000001</v>
-      </c>
-      <c r="F38" s="3">
-        <v>2.5316000000000001</v>
-      </c>
-      <c r="G38" s="2">
-        <f t="shared" si="1"/>
         <v>2.0192000000000001</v>
       </c>
-      <c r="H38" s="3"/>
+      <c r="H38" s="5"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>110</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="4">
+        <f t="shared" si="3"/>
+        <v>34.375</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0.55159999999999998</v>
+      </c>
+      <c r="E39" s="5">
+        <v>2.5701999999999998</v>
+      </c>
+      <c r="F39" s="5">
+        <v>2.5390000000000001</v>
+      </c>
+      <c r="G39" s="4">
         <f t="shared" si="2"/>
-        <v>34.375</v>
-      </c>
-      <c r="D39" s="3">
-        <v>0.55160000000000009</v>
-      </c>
-      <c r="E39" s="3">
-        <v>2.5701999999999998</v>
-      </c>
-      <c r="F39" s="3">
-        <v>2.5390000000000001</v>
-      </c>
-      <c r="G39" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0185999999999997</v>
-      </c>
-      <c r="H39" s="3"/>
+        <v>2.0186000000000002</v>
+      </c>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>120</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="4">
+        <f t="shared" si="3"/>
+        <v>35.294117647058798</v>
+      </c>
+      <c r="D40" s="5">
+        <v>0.55649999999999999</v>
+      </c>
+      <c r="E40" s="5">
+        <v>2.5743</v>
+      </c>
+      <c r="F40" s="5">
+        <v>2.5446</v>
+      </c>
+      <c r="G40" s="4">
         <f t="shared" si="2"/>
-        <v>35.294117647058819</v>
-      </c>
-      <c r="D40" s="3">
-        <v>0.55650000000000022</v>
-      </c>
-      <c r="E40" s="3">
-        <v>2.5743</v>
-      </c>
-      <c r="F40" s="3">
-        <v>2.5446</v>
-      </c>
-      <c r="G40" s="2">
-        <f t="shared" si="1"/>
         <v>2.0177999999999998</v>
       </c>
-      <c r="H40" s="3"/>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>130</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="4">
+        <f t="shared" si="3"/>
+        <v>36.1111111111111</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0.56010000000000004</v>
+      </c>
+      <c r="E41" s="5">
+        <v>2.5716000000000001</v>
+      </c>
+      <c r="F41" s="5">
+        <v>2.5488</v>
+      </c>
+      <c r="G41" s="4">
         <f t="shared" si="2"/>
-        <v>36.111111111111107</v>
-      </c>
-      <c r="D41" s="3">
-        <v>0.56009999999999982</v>
-      </c>
-      <c r="E41" s="3">
-        <v>2.5716000000000001</v>
-      </c>
-      <c r="F41" s="3">
-        <v>2.5488</v>
-      </c>
-      <c r="G41" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0115000000000003</v>
-      </c>
-      <c r="H41" s="3"/>
+        <v>2.0114999999999998</v>
+      </c>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>140</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="4">
+        <f t="shared" si="3"/>
+        <v>36.842105263157897</v>
+      </c>
+      <c r="D42" s="5">
+        <v>0.56579999999999997</v>
+      </c>
+      <c r="E42" s="5">
+        <v>2.5832000000000002</v>
+      </c>
+      <c r="F42" s="5">
+        <v>2.5537000000000001</v>
+      </c>
+      <c r="G42" s="4">
         <f t="shared" si="2"/>
-        <v>36.842105263157897</v>
-      </c>
-      <c r="D42" s="3">
-        <v>0.56579999999999986</v>
-      </c>
-      <c r="E42" s="3">
-        <v>2.5832000000000002</v>
-      </c>
-      <c r="F42" s="3">
-        <v>2.5537000000000001</v>
-      </c>
-      <c r="G42" s="2">
-        <f t="shared" si="1"/>
-        <v>2.0174000000000003</v>
-      </c>
-      <c r="H42" s="3"/>
+        <v>2.0173999999999999</v>
+      </c>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>150</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="4">
+        <f t="shared" si="3"/>
+        <v>37.5</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0.56740000000000002</v>
+      </c>
+      <c r="E43" s="5">
+        <v>2.5868000000000002</v>
+      </c>
+      <c r="F43" s="5">
+        <v>2.5537000000000001</v>
+      </c>
+      <c r="G43" s="4">
         <f t="shared" si="2"/>
-        <v>37.5</v>
-      </c>
-      <c r="D43" s="3">
-        <v>0.56740000000000013</v>
-      </c>
-      <c r="E43" s="3">
-        <v>2.5868000000000002</v>
-      </c>
-      <c r="F43" s="3">
-        <v>2.5537000000000001</v>
-      </c>
-      <c r="G43" s="2">
-        <f t="shared" si="1"/>
         <v>2.0194000000000001</v>
       </c>
-      <c r="H43" s="3"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>160</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="4">
+        <f t="shared" si="3"/>
+        <v>38.095238095238102</v>
+      </c>
+      <c r="D44" s="5">
+        <v>0.57150000000000001</v>
+      </c>
+      <c r="E44" s="5">
+        <v>2.5846</v>
+      </c>
+      <c r="F44" s="5">
+        <v>2.5596000000000001</v>
+      </c>
+      <c r="G44" s="4">
         <f t="shared" si="2"/>
-        <v>38.095238095238095</v>
-      </c>
-      <c r="D44" s="3">
-        <v>0.5714999999999999</v>
-      </c>
-      <c r="E44" s="3">
-        <v>2.5846</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2.5596000000000001</v>
-      </c>
-      <c r="G44" s="2">
-        <f t="shared" si="1"/>
         <v>2.0131000000000001</v>
       </c>
-      <c r="H44" s="3"/>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>170</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="4">
+        <f t="shared" si="3"/>
+        <v>38.636363636363598</v>
+      </c>
+      <c r="D45" s="5">
+        <v>0.57279999999999998</v>
+      </c>
+      <c r="E45" s="5">
+        <v>2.59</v>
+      </c>
+      <c r="F45" s="5">
+        <v>2.5615999999999999</v>
+      </c>
+      <c r="G45" s="4">
         <f t="shared" si="2"/>
-        <v>38.636363636363633</v>
-      </c>
-      <c r="D45" s="3">
-        <v>0.57279999999999998</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2.59</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2.5615999999999999</v>
-      </c>
-      <c r="G45" s="2">
-        <f t="shared" si="1"/>
         <v>2.0171999999999999</v>
       </c>
-      <c r="H45" s="3"/>
+      <c r="H45" s="5"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>180</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="4">
+        <f t="shared" si="3"/>
+        <v>39.130434782608702</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="4">
         <f t="shared" si="2"/>
-        <v>39.130434782608695</v>
-      </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="2">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H46" s="3"/>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>190</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="4">
+        <f t="shared" si="3"/>
+        <v>39.5833333333333</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="4">
         <f t="shared" si="2"/>
-        <v>39.583333333333336</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="2">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="3"/>
+      <c r="H47" s="5"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>200</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="4">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="4">
         <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="2">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="3"/>
+      <c r="H48" s="5"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G51" s="2">
+      <c r="G51" s="4">
         <f>AVERAGE(G53:G73)</f>
-        <v>2.020423809523809</v>
+        <v>2.0204238095238098</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="17" x14ac:dyDescent="0.2">
@@ -6181,507 +7362,507 @@
       <c r="F52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>5</v>
+      <c r="G52" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>0</v>
       </c>
-      <c r="D53" s="2">
-        <v>5.1699999999999857E-2</v>
-      </c>
-      <c r="E53" s="2">
+      <c r="D53" s="4">
+        <v>5.1699999999999899E-2</v>
+      </c>
+      <c r="E53" s="4">
         <v>2.0722999999999998</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="4">
         <v>1.9874000000000001</v>
       </c>
-      <c r="G53" s="2">
-        <f t="shared" ref="G53:G74" si="3">MAX((E53-D53),(D53-F53))</f>
+      <c r="G53" s="4">
+        <f t="shared" ref="G53:G74" si="4">MAX((E53-D53),(D53-F53))</f>
         <v>2.0206</v>
       </c>
-      <c r="H53" s="3"/>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54">
         <v>10</v>
       </c>
-      <c r="C54" s="2">
-        <f>1/((1/C$1)+(1/$B54))</f>
-        <v>9.0909090909090917</v>
-      </c>
-      <c r="D54" s="2">
-        <v>0.37360000000000015</v>
-      </c>
-      <c r="E54" s="2">
+      <c r="C54" s="4">
+        <f t="shared" ref="C54:C73" si="5">1/((1/C$1)+(1/$B54))</f>
+        <v>9.0909090909090899</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0.37359999999999999</v>
+      </c>
+      <c r="E54" s="4">
         <v>2.3942000000000001</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="4">
         <v>2.3578999999999999</v>
       </c>
-      <c r="G54" s="2">
-        <f t="shared" si="3"/>
+      <c r="G54" s="4">
+        <f t="shared" si="4"/>
         <v>2.0206</v>
       </c>
-      <c r="H54" s="3"/>
+      <c r="H54" s="5"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>20</v>
       </c>
-      <c r="C55" s="2">
-        <f>1/((1/C$1)+(1/$B55))</f>
-        <v>16.666666666666664</v>
-      </c>
-      <c r="D55" s="2">
+      <c r="C55" s="4">
+        <f t="shared" si="5"/>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="D55" s="4">
         <v>0.51239999999999997</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="4">
         <v>2.5324</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="4">
         <v>2.4967999999999999</v>
       </c>
-      <c r="G55" s="2">
-        <f t="shared" si="3"/>
+      <c r="G55" s="4">
+        <f t="shared" si="4"/>
         <v>2.02</v>
       </c>
-      <c r="H55" s="3"/>
+      <c r="H55" s="5"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56">
         <v>30</v>
       </c>
-      <c r="C56" s="2">
-        <f>1/((1/C$1)+(1/$B56))</f>
-        <v>23.076923076923077</v>
-      </c>
-      <c r="D56" s="2">
+      <c r="C56" s="4">
+        <f t="shared" si="5"/>
+        <v>23.076923076923102</v>
+      </c>
+      <c r="D56" s="4">
         <v>0.58689999999999998</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="4">
         <v>2.6074999999999999</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="4">
         <v>2.5731000000000002</v>
       </c>
-      <c r="G56" s="2">
-        <f t="shared" si="3"/>
+      <c r="G56" s="4">
+        <f t="shared" si="4"/>
         <v>2.0206</v>
       </c>
-      <c r="H56" s="3"/>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>40</v>
       </c>
-      <c r="C57" s="2">
-        <f>1/((1/C$1)+(1/$B57))</f>
-        <v>28.571428571428569</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0.63249999999999984</v>
-      </c>
-      <c r="E57" s="2">
+      <c r="C57" s="4">
+        <f t="shared" si="5"/>
+        <v>28.571428571428601</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0.63249999999999995</v>
+      </c>
+      <c r="E57" s="4">
         <v>2.6636000000000002</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="4">
         <v>2.6187</v>
       </c>
-      <c r="G57" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0311000000000003</v>
-      </c>
-      <c r="H57" s="3"/>
+      <c r="G57" s="4">
+        <f t="shared" si="4"/>
+        <v>2.0310999999999999</v>
+      </c>
+      <c r="H57" s="5"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>50</v>
       </c>
-      <c r="C58" s="2">
-        <f>1/((1/C$1)+(1/$B58))</f>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0.66210000000000013</v>
-      </c>
-      <c r="E58" s="2">
+      <c r="C58" s="4">
+        <f t="shared" si="5"/>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0.66210000000000002</v>
+      </c>
+      <c r="E58" s="4">
         <v>2.6829999999999998</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="4">
         <v>2.6488999999999998</v>
       </c>
-      <c r="G58" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0208999999999997</v>
-      </c>
-      <c r="H58" s="3"/>
+      <c r="G58" s="4">
+        <f t="shared" si="4"/>
+        <v>2.0209000000000001</v>
+      </c>
+      <c r="H58" s="5"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>60</v>
       </c>
-      <c r="C59" s="2">
-        <f>1/((1/C$1)+(1/$B59))</f>
+      <c r="C59" s="4">
+        <f t="shared" si="5"/>
         <v>37.5</v>
       </c>
-      <c r="D59" s="2">
-        <v>0.68449999999999989</v>
-      </c>
-      <c r="E59" s="2">
+      <c r="D59" s="4">
+        <v>0.6845</v>
+      </c>
+      <c r="E59" s="4">
         <v>2.7017000000000002</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="4">
         <v>2.6737000000000002</v>
       </c>
-      <c r="G59" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0172000000000003</v>
-      </c>
-      <c r="H59" s="3"/>
+      <c r="G59" s="4">
+        <f t="shared" si="4"/>
+        <v>2.0171999999999999</v>
+      </c>
+      <c r="H59" s="5"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>70</v>
       </c>
-      <c r="C60" s="2">
-        <f>1/((1/C$1)+(1/$B60))</f>
+      <c r="C60" s="4">
+        <f t="shared" si="5"/>
         <v>41.176470588235297</v>
       </c>
-      <c r="D60" s="2">
-        <v>0.6987000000000001</v>
-      </c>
-      <c r="E60" s="2">
+      <c r="D60" s="4">
+        <v>0.69869999999999999</v>
+      </c>
+      <c r="E60" s="4">
         <v>2.7216</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="4">
         <v>2.6833</v>
       </c>
-      <c r="G60" s="2">
-        <f t="shared" si="3"/>
+      <c r="G60" s="4">
+        <f t="shared" si="4"/>
         <v>2.0228999999999999</v>
       </c>
-      <c r="H60" s="3"/>
+      <c r="H60" s="5"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>80</v>
       </c>
-      <c r="C61" s="2">
-        <f>1/((1/C$1)+(1/$B61))</f>
-        <v>44.444444444444443</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="C61" s="4">
+        <f t="shared" si="5"/>
+        <v>44.4444444444444</v>
+      </c>
+      <c r="D61" s="4">
         <v>0.70979999999999999</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="4">
         <v>2.7311000000000001</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="4">
         <v>2.6945999999999999</v>
       </c>
-      <c r="G61" s="2">
-        <f t="shared" si="3"/>
+      <c r="G61" s="4">
+        <f t="shared" si="4"/>
         <v>2.0213000000000001</v>
       </c>
-      <c r="H61" s="3"/>
+      <c r="H61" s="5"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>90</v>
       </c>
-      <c r="C62" s="2">
-        <f>1/((1/C$1)+(1/$B62))</f>
-        <v>47.368421052631575</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0.71700000000000008</v>
-      </c>
-      <c r="E62" s="2">
+      <c r="C62" s="4">
+        <f t="shared" si="5"/>
+        <v>47.368421052631597</v>
+      </c>
+      <c r="D62" s="4">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="E62" s="4">
         <v>2.7402000000000002</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="4">
         <v>2.7014</v>
       </c>
-      <c r="G62" s="2">
-        <f t="shared" si="3"/>
+      <c r="G62" s="4">
+        <f t="shared" si="4"/>
         <v>2.0232000000000001</v>
       </c>
-      <c r="H62" s="3"/>
+      <c r="H62" s="5"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63">
         <v>100</v>
       </c>
-      <c r="C63" s="2">
-        <f>1/((1/C$1)+(1/$B63))</f>
+      <c r="C63" s="4">
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D63" s="2">
-        <v>0.72319999999999984</v>
-      </c>
-      <c r="E63" s="2">
+      <c r="D63" s="4">
+        <v>0.72319999999999995</v>
+      </c>
+      <c r="E63" s="4">
         <v>2.7450999999999999</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="4">
         <v>2.7088000000000001</v>
       </c>
-      <c r="G63" s="2">
-        <f t="shared" si="3"/>
+      <c r="G63" s="4">
+        <f t="shared" si="4"/>
         <v>2.0219</v>
       </c>
-      <c r="H63" s="3"/>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>110</v>
       </c>
-      <c r="C64" s="2">
-        <f>1/((1/C$1)+(1/$B64))</f>
-        <v>52.380952380952387</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0.72889999999999988</v>
-      </c>
-      <c r="E64" s="2">
+      <c r="C64" s="4">
+        <f t="shared" si="5"/>
+        <v>52.380952380952401</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0.72889999999999999</v>
+      </c>
+      <c r="E64" s="4">
         <v>2.7507999999999999</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="4">
         <v>2.7149999999999999</v>
       </c>
-      <c r="G64" s="2">
-        <f t="shared" si="3"/>
+      <c r="G64" s="4">
+        <f t="shared" si="4"/>
         <v>2.0219</v>
       </c>
-      <c r="H64" s="3"/>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>120</v>
       </c>
-      <c r="C65" s="2">
-        <f>1/((1/C$1)+(1/$B65))</f>
-        <v>54.545454545454547</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0.73280000000000012</v>
-      </c>
-      <c r="E65" s="2">
+      <c r="C65" s="4">
+        <f t="shared" si="5"/>
+        <v>54.545454545454497</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0.73280000000000001</v>
+      </c>
+      <c r="E65" s="4">
         <v>2.7524999999999999</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="4">
         <v>2.7195999999999998</v>
       </c>
-      <c r="G65" s="2">
-        <f>MAX((E65-D65),(D65-F65))</f>
+      <c r="G65" s="4">
+        <f t="shared" si="4"/>
         <v>2.0196999999999998</v>
       </c>
-      <c r="H65" s="3"/>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>130</v>
       </c>
-      <c r="C66" s="2">
-        <f>1/((1/C$1)+(1/$B66))</f>
-        <v>56.521739130434774</v>
-      </c>
-      <c r="D66" s="2">
-        <v>0.73579999999999979</v>
-      </c>
-      <c r="E66" s="2">
+      <c r="C66" s="4">
+        <f t="shared" si="5"/>
+        <v>56.521739130434803</v>
+      </c>
+      <c r="D66" s="4">
+        <v>0.73580000000000001</v>
+      </c>
+      <c r="E66" s="4">
         <v>2.7542</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="4">
         <v>2.7221000000000002</v>
       </c>
-      <c r="G66" s="2">
-        <f>MAX((E66-D66),(D66-F66))</f>
+      <c r="G66" s="4">
+        <f t="shared" si="4"/>
         <v>2.0184000000000002</v>
       </c>
-      <c r="H66" s="3"/>
+      <c r="H66" s="5"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>140</v>
       </c>
-      <c r="C67" s="2">
-        <f>1/((1/C$1)+(1/$B67))</f>
-        <v>58.333333333333329</v>
-      </c>
-      <c r="D67" s="2">
-        <v>0.73850000000000016</v>
-      </c>
-      <c r="E67" s="2">
+      <c r="C67" s="4">
+        <f t="shared" si="5"/>
+        <v>58.3333333333333</v>
+      </c>
+      <c r="D67" s="4">
+        <v>0.73850000000000005</v>
+      </c>
+      <c r="E67" s="4">
         <v>2.7557</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="4">
         <v>2.7265000000000001</v>
       </c>
-      <c r="G67" s="2">
-        <f t="shared" si="3"/>
+      <c r="G67" s="4">
+        <f t="shared" si="4"/>
         <v>2.0171999999999999</v>
       </c>
-      <c r="H67" s="3"/>
+      <c r="H67" s="5"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>150</v>
       </c>
-      <c r="C68" s="2">
-        <f>1/((1/C$1)+(1/$B68))</f>
+      <c r="C68" s="4">
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="D68" s="2">
-        <v>0.74069999999999991</v>
-      </c>
-      <c r="E68" s="2">
+      <c r="D68" s="4">
+        <v>0.74070000000000003</v>
+      </c>
+      <c r="E68" s="4">
         <v>2.7608000000000001</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="4">
         <v>2.7277</v>
       </c>
-      <c r="G68" s="2">
-        <f t="shared" si="3"/>
-        <v>2.0201000000000002</v>
-      </c>
-      <c r="H68" s="3"/>
+      <c r="G68" s="4">
+        <f t="shared" si="4"/>
+        <v>2.0200999999999998</v>
+      </c>
+      <c r="H68" s="5"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>160</v>
       </c>
-      <c r="C69" s="2">
-        <f>1/((1/C$1)+(1/$B69))</f>
-        <v>61.538461538461533</v>
-      </c>
-      <c r="D69" s="2">
-        <v>0.74359999999999982</v>
-      </c>
-      <c r="E69" s="2">
+      <c r="C69" s="4">
+        <f t="shared" si="5"/>
+        <v>61.538461538461497</v>
+      </c>
+      <c r="D69" s="4">
+        <v>0.74360000000000004</v>
+      </c>
+      <c r="E69" s="4">
         <v>2.7627999999999999</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="4">
         <v>2.7302</v>
       </c>
-      <c r="G69" s="2">
-        <f t="shared" si="3"/>
+      <c r="G69" s="4">
+        <f t="shared" si="4"/>
         <v>2.0192000000000001</v>
       </c>
-      <c r="H69" s="3"/>
+      <c r="H69" s="5"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70">
         <v>170</v>
       </c>
-      <c r="C70" s="2">
-        <f>1/((1/C$1)+(1/$B70))</f>
-        <v>62.962962962962955</v>
-      </c>
-      <c r="D70" s="2">
-        <v>0.74449999999999994</v>
-      </c>
-      <c r="E70" s="2">
+      <c r="C70" s="4">
+        <f t="shared" si="5"/>
+        <v>62.962962962962997</v>
+      </c>
+      <c r="D70" s="4">
+        <v>0.74450000000000005</v>
+      </c>
+      <c r="E70" s="4">
         <v>2.7616000000000001</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="4">
         <v>2.7277</v>
       </c>
-      <c r="G70" s="2">
-        <f t="shared" si="3"/>
+      <c r="G70" s="4">
+        <f t="shared" si="4"/>
         <v>2.0171000000000001</v>
       </c>
-      <c r="H70" s="3"/>
+      <c r="H70" s="5"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>180</v>
       </c>
-      <c r="C71" s="2">
-        <f>1/((1/C$1)+(1/$B71))</f>
-        <v>64.285714285714292</v>
-      </c>
-      <c r="D71" s="2">
-        <v>0.7448999999999999</v>
-      </c>
-      <c r="E71" s="2">
+      <c r="C71" s="4">
+        <f t="shared" si="5"/>
+        <v>64.285714285714306</v>
+      </c>
+      <c r="D71" s="4">
+        <v>0.74490000000000001</v>
+      </c>
+      <c r="E71" s="4">
         <v>2.7612999999999999</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="4">
         <v>2.7303999999999999</v>
       </c>
-      <c r="G71" s="2">
-        <f t="shared" si="3"/>
+      <c r="G71" s="4">
+        <f t="shared" si="4"/>
         <v>2.0164</v>
       </c>
-      <c r="H71" s="3"/>
+      <c r="H71" s="5"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>190</v>
       </c>
-      <c r="C72" s="2">
-        <f>1/((1/C$1)+(1/$B72))</f>
-        <v>65.517241379310335</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="C72" s="4">
+        <f t="shared" si="5"/>
+        <v>65.517241379310306</v>
+      </c>
+      <c r="D72" s="4">
         <v>0.74639999999999995</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="4">
         <v>2.7643</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="4">
         <v>2.7330999999999999</v>
       </c>
-      <c r="G72" s="2">
-        <f t="shared" si="3"/>
+      <c r="G72" s="4">
+        <f t="shared" si="4"/>
         <v>2.0179</v>
       </c>
-      <c r="H72" s="3"/>
+      <c r="H72" s="5"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>200</v>
       </c>
-      <c r="C73" s="2">
-        <f>1/((1/C$1)+(1/$B73))</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="D73" s="2">
+      <c r="C73" s="4">
+        <f t="shared" si="5"/>
+        <v>66.6666666666667</v>
+      </c>
+      <c r="D73" s="4">
         <v>0.74770000000000003</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="4">
         <v>2.7684000000000002</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="4">
         <v>2.7338</v>
       </c>
-      <c r="G73" s="2">
-        <f t="shared" si="3"/>
+      <c r="G73" s="4">
+        <f t="shared" si="4"/>
         <v>2.0207000000000002</v>
       </c>
-      <c r="H73" s="3"/>
+      <c r="H73" s="5"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="4">
         <v>0.77039999999999997</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="4">
         <v>2.7915000000000001</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="4">
         <v>2.7536999999999998</v>
       </c>
-      <c r="G74" s="2">
-        <f t="shared" si="3"/>
+      <c r="G74" s="4">
+        <f t="shared" si="4"/>
         <v>2.0211000000000001</v>
       </c>
-      <c r="H74" s="3"/>
+      <c r="H74" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6690,31 +7871,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB36A28-B9C3-6B42-8C48-B699222704BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6727,19 +7908,19 @@
       </c>
       <c r="D2">
         <f>2.2/1000000000</f>
-        <v>2.2000000000000003E-9</v>
+        <v>2.1999999999999998E-9</v>
       </c>
       <c r="E2">
         <f>1.4/((B2+(2*C2))*D2)/1000</f>
-        <v>52.160953800298053</v>
-      </c>
-      <c r="F2" s="7">
+        <v>52.160953800298103</v>
+      </c>
+      <c r="F2" s="3">
         <f>100*(B2+C2)/(B2+(2*C2))</f>
-        <v>54.098360655737707</v>
-      </c>
-      <c r="G2" s="7">
+        <v>54.0983606557377</v>
+      </c>
+      <c r="G2" s="3">
         <f>100*B2/(B2+C2)</f>
-        <v>15.151515151515152</v>
+        <v>15.1515151515152</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
@@ -6751,22 +7932,214 @@
       </c>
       <c r="D3">
         <f>2.2/1000000000</f>
-        <v>2.2000000000000003E-9</v>
+        <v>2.1999999999999998E-9</v>
       </c>
       <c r="E3">
         <f>1.4/((B3+(2*C3))*D3)/1000</f>
-        <v>14.14141414141414</v>
-      </c>
-      <c r="F3" s="7">
+        <v>14.141414141414099</v>
+      </c>
+      <c r="F3" s="3">
         <f>100*(B3+C3)/(B3+(2*C3))</f>
-        <v>51.111111111111114</v>
-      </c>
-      <c r="G3" s="7">
+        <v>51.1111111111111</v>
+      </c>
+      <c r="G3" s="3">
         <f>100*B3/(B3+C3)</f>
-        <v>4.3478260869565215</v>
+        <v>4.3478260869565197</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1.9E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>0.3982</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>0.78859999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>1.1043000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>1.3263</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>1.5224</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>1.6637999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>1.7959000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>1.8996999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>90</v>
+      </c>
+      <c r="C12">
+        <v>1.9927999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>2.0655000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>110</v>
+      </c>
+      <c r="C14">
+        <v>2.1444000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>120</v>
+      </c>
+      <c r="C15">
+        <v>2.2038000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>130</v>
+      </c>
+      <c r="C16">
+        <v>2.2563</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>140</v>
+      </c>
+      <c r="C17">
+        <v>2.3071000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>150</v>
+      </c>
+      <c r="C18">
+        <v>2.3546</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>160</v>
+      </c>
+      <c r="C19">
+        <v>2.3933</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>170</v>
+      </c>
+      <c r="C20">
+        <v>2.4276</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>180</v>
+      </c>
+      <c r="C21">
+        <v>2.4626999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>190</v>
+      </c>
+      <c r="C22">
+        <v>2.4944000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>200</v>
+      </c>
+      <c r="C23">
+        <v>2.5204</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E25" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/archive/REM - Vsense.xlsx
+++ b/archive/REM - Vsense.xlsx
@@ -8,25 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/margabudi/Documents/hardware/ESU/archive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2ED8972-4586-9A4E-803D-28292FB1E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BBAD44-A418-6840-9D6F-47C3735D38F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId5"/>
+    <sheet name="REM-7.0 CUT 1" sheetId="7" r:id="rId6"/>
+    <sheet name="REM-7.0 CUT 2" sheetId="8" r:id="rId7"/>
+    <sheet name="REM-7.0 CUT 3" sheetId="9" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet4!$B$3:$B$23</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet4!$C$2</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet4!$C$3:$C$23</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet4!$B$2</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet4!$B$3:$B$23</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet4!$C$2</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet4!$C$3:$C$23</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="16">
   <si>
     <t>R</t>
   </si>
@@ -148,6 +143,12 @@
   <si>
     <t>REM Test Results Under Varying Input Resistance</t>
   </si>
+  <si>
+    <t>R [Ω]</t>
+  </si>
+  <si>
+    <t>P [W]</t>
+  </si>
 </sst>
 </file>
 
@@ -189,18 +190,76 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -211,7 +270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -230,13 +289,37 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,7 +830,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5C3D-9049-BAE8-06B7D9ACF873}"/>
+              <c16:uniqueId val="{00000001-FF37-BA45-AA64-89C06E908EB5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -941,7 +1024,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-5C3D-9049-BAE8-06B7D9ACF873}"/>
+              <c16:uniqueId val="{00000003-FF37-BA45-AA64-89C06E908EB5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1144,7 +1227,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-5C3D-9049-BAE8-06B7D9ACF873}"/>
+              <c16:uniqueId val="{00000005-FF37-BA45-AA64-89C06E908EB5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1629,7 +1712,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5608-4E46-B3C3-F802B661FBE2}"/>
+              <c16:uniqueId val="{00000001-47DE-1445-B223-EB18B44ED8E5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1823,7 +1906,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-5608-4E46-B3C3-F802B661FBE2}"/>
+              <c16:uniqueId val="{00000003-47DE-1445-B223-EB18B44ED8E5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2026,7 +2109,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-5608-4E46-B3C3-F802B661FBE2}"/>
+              <c16:uniqueId val="{00000005-47DE-1445-B223-EB18B44ED8E5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2437,7 +2520,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5549-9440-880A-6851A07CEDA2}"/>
+              <c16:uniqueId val="{00000000-7836-F34D-BF7B-B125F8054DF3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2495,7 +2578,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2527,7 +2610,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2565,7 +2648,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2628,7 +2711,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2660,7 +2743,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2698,7 +2781,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2730,6 +2813,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{f045cee0-8cc9-4c20-bbb7-ba77d7e8469a}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2751,7 +2839,2155 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VRMS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet5!$B$3:$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet5!$C$3:$C$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>1.9E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3982</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78859999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1043000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3263</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5224</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6637999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7959000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8996999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9927999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0655000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1444000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2038000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2563</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3071000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3546</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3933</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4276</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4626999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4944000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5204</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1569-4A4D-8A8A-FDF2D8196626}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2054039616"/>
+        <c:axId val="2054037824"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2054039616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Resistance [Ω]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054037824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054037824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Voltage [V]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054039616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{f045cee0-8cc9-4c20-bbb7-ba77d7e8469a}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'REM-7.0 CUT 1'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VRMS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'REM-7.0 CUT 1'!$B$4:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'REM-7.0 CUT 1'!$C$4:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>1.9E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3982</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78859999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1043000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3263</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5224</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6637999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7959000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8996999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9927999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0655000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1444000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2038000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2563</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3071000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3546</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3933</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4276</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4626999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4944000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5204</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C45D-A34E-810A-C4D50C01E799}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2054039616"/>
+        <c:axId val="2054037824"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2054039616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Resistance [Ω]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054037824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054037824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Voltage [V]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054039616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{f045cee0-8cc9-4c20-bbb7-ba77d7e8469a}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'REM-7.0 CUT 2'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VRMS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'REM-7.0 CUT 2'!$B$4:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'REM-7.0 CUT 2'!$C$4:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>1.9E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3982</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78859999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1043000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3263</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5224</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6637999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7959000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8996999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9927999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0655000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1444000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2038000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2563</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3071000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3546</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3933</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4276</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4626999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4944000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5204</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3FD8-7841-99E1-934EEB948049}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2054039616"/>
+        <c:axId val="2054037824"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2054039616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Resistance [Ω]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054037824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054037824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Voltage [V]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054039616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{f045cee0-8cc9-4c20-bbb7-ba77d7e8469a}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'REM-7.0 CUT 3'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VRMS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'REM-7.0 CUT 3'!$B$4:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'REM-7.0 CUT 3'!$C$4:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>1.9E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3982</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78859999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1043000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3263</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5224</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6637999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7959000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8996999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9927999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0655000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1444000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2038000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.2563</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3071000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3546</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.3933</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4276</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4626999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.4944000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5204</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2889-B048-9552-D666F4BA2B63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2054039616"/>
+        <c:axId val="2054037824"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2054039616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Resistance [Ω]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054037824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2054037824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Voltage [V]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2054039616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.5"/>
+        <c:minorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{f045cee0-8cc9-4c20-bbb7-ba77d7e8469a}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -2884,6 +5120,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3917,6 +6313,2070 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4534,7 +8994,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A59C0DB-8F25-4783-3BB0-D2518CB5242B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4550,6 +9010,345 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>679623</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>185351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>679623</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>6864</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>81863</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>686313</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>824217</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3207</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CD1C4CC-8E43-F237-14E5-E3CB63CF34C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="686313" y="218081"/>
+          <a:ext cx="824217" cy="378434"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>81863</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B081DE10-B1B7-F241-AA99-F67C75A0D567}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>686313</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>824217</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3207</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A82CF161-8DC2-164E-84E2-DEDF8AF70CD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="686313" y="219107"/>
+          <a:ext cx="823704" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>12065</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>81863</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3853ED6-5BE5-AE42-ABEC-63D2BE7E40C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>686313</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>824217</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3207</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5910A53-9901-6644-A08E-3C3D78246C4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="686313" y="219107"/>
+          <a:ext cx="823704" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4843,7 +9642,7 @@
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -5352,10 +10151,10 @@
       <c r="F27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5820,7 +10619,7 @@
       <c r="F52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6005,7 +10804,7 @@
         <f>N60-M60</f>
         <v>6.1300000000000097E-2</v>
       </c>
-      <c r="P60" s="7">
+      <c r="P60" s="6">
         <f>D63-D58</f>
         <v>6.1099999999999703E-2</v>
       </c>
@@ -6307,7 +11106,7 @@
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B74" s="2" t="s">
+      <c r="B74" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="4">
@@ -6362,7 +11161,7 @@
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -6873,10 +11672,10 @@
       <c r="F27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7362,7 +12161,7 @@
       <c r="F52" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7846,7 +12645,7 @@
       <c r="H73" s="5"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B74" s="2" t="s">
+      <c r="B74" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="4">
@@ -7880,22 +12679,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -8134,7 +12933,7 @@
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8142,4 +12941,1615 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1.9E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>0.3982</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>0.78859999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>1.1043000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>1.3263</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>1.5224</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>1.6637999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>1.7959000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>1.8996999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>90</v>
+      </c>
+      <c r="C12">
+        <v>1.9927999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>2.0655000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>110</v>
+      </c>
+      <c r="C14">
+        <v>2.1444000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>120</v>
+      </c>
+      <c r="C15">
+        <v>2.2038000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>130</v>
+      </c>
+      <c r="C16">
+        <v>2.2563</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>140</v>
+      </c>
+      <c r="C17">
+        <v>2.3071000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>150</v>
+      </c>
+      <c r="C18">
+        <v>2.3546</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>160</v>
+      </c>
+      <c r="C19">
+        <v>2.3933</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>170</v>
+      </c>
+      <c r="C20">
+        <v>2.4276</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>180</v>
+      </c>
+      <c r="C21">
+        <v>2.4626999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>190</v>
+      </c>
+      <c r="C22">
+        <v>2.4944000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>200</v>
+      </c>
+      <c r="C23">
+        <v>2.5204</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B1:O26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="7"/>
+    <col min="2" max="2" width="10.83203125" style="7" customWidth="1"/>
+    <col min="3" max="13" width="8.83203125" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12">
+        <v>20</v>
+      </c>
+      <c r="F2" s="12">
+        <v>30</v>
+      </c>
+      <c r="G2" s="12">
+        <v>40</v>
+      </c>
+      <c r="H2" s="12">
+        <v>50</v>
+      </c>
+      <c r="I2" s="12">
+        <v>60</v>
+      </c>
+      <c r="J2" s="12">
+        <v>70</v>
+      </c>
+      <c r="K2" s="12">
+        <v>80</v>
+      </c>
+      <c r="L2" s="12">
+        <v>90</v>
+      </c>
+      <c r="M2" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B4" s="9">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.9E-3</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="8">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.3982</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="8">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B7" s="8">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.1043000000000001</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B8" s="8">
+        <v>40</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.3263</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="8">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.5224</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="8">
+        <v>60</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1.6637999999999999</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="8">
+        <v>70</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.7959000000000001</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="8">
+        <v>80</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1.8996999999999999</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
+        <v>90</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1.9927999999999999</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B14" s="8">
+        <v>100</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2.0655000000000001</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B15" s="8">
+        <v>110</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.1444000000000001</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B16" s="8">
+        <v>120</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.2038000000000002</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" s="8">
+        <v>130</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.2563</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" s="8">
+        <v>140</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.3071000000000002</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19" s="8">
+        <v>150</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2.3546</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20" s="8">
+        <v>160</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2.3933</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" s="8">
+        <v>170</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.4276</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" s="8">
+        <v>180</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2.4626999999999999</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" s="8">
+        <v>190</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2.4944000000000002</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" s="8">
+        <v>200</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2.5204</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4A5FC4-9DE0-A747-B92F-8FB4B911C08A}">
+  <dimension ref="B1:O26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="7"/>
+    <col min="2" max="2" width="10.83203125" style="7" customWidth="1"/>
+    <col min="3" max="13" width="8.83203125" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12">
+        <v>20</v>
+      </c>
+      <c r="F2" s="12">
+        <v>30</v>
+      </c>
+      <c r="G2" s="12">
+        <v>40</v>
+      </c>
+      <c r="H2" s="12">
+        <v>50</v>
+      </c>
+      <c r="I2" s="12">
+        <v>60</v>
+      </c>
+      <c r="J2" s="12">
+        <v>70</v>
+      </c>
+      <c r="K2" s="12">
+        <v>80</v>
+      </c>
+      <c r="L2" s="12">
+        <v>90</v>
+      </c>
+      <c r="M2" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B4" s="9">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.9E-3</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="8">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.3982</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="8">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B7" s="8">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.1043000000000001</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B8" s="8">
+        <v>40</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.3263</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="8">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.5224</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="8">
+        <v>60</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1.6637999999999999</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="8">
+        <v>70</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.7959000000000001</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="8">
+        <v>80</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1.8996999999999999</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
+        <v>90</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1.9927999999999999</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B14" s="8">
+        <v>100</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2.0655000000000001</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B15" s="8">
+        <v>110</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.1444000000000001</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B16" s="8">
+        <v>120</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.2038000000000002</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" s="8">
+        <v>130</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.2563</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" s="8">
+        <v>140</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.3071000000000002</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19" s="8">
+        <v>150</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2.3546</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20" s="8">
+        <v>160</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2.3933</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" s="8">
+        <v>170</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.4276</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" s="8">
+        <v>180</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2.4626999999999999</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" s="8">
+        <v>190</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2.4944000000000002</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" s="8">
+        <v>200</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2.5204</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C285355-FD6C-6E49-89BA-D61B28825BDE}">
+  <dimension ref="B1:O37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="7"/>
+    <col min="2" max="2" width="10.83203125" style="7" customWidth="1"/>
+    <col min="3" max="13" width="8.83203125" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12">
+        <v>20</v>
+      </c>
+      <c r="F2" s="12">
+        <v>30</v>
+      </c>
+      <c r="G2" s="12">
+        <v>40</v>
+      </c>
+      <c r="H2" s="12">
+        <v>50</v>
+      </c>
+      <c r="I2" s="12">
+        <v>60</v>
+      </c>
+      <c r="J2" s="12">
+        <v>70</v>
+      </c>
+      <c r="K2" s="12">
+        <v>80</v>
+      </c>
+      <c r="L2" s="12">
+        <v>90</v>
+      </c>
+      <c r="M2" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B4" s="9">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.9E-3</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="8">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.3982</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="8">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B7" s="8">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.1043000000000001</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B8" s="8">
+        <v>40</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.3263</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="8">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.5224</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="8">
+        <v>60</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1.6637999999999999</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="8">
+        <v>70</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.7959000000000001</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="8">
+        <v>80</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1.8996999999999999</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
+        <v>90</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1.9927999999999999</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B14" s="8">
+        <v>100</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2.0655000000000001</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B15" s="8">
+        <v>110</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.1444000000000001</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B16" s="8">
+        <v>120</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.2038000000000002</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" s="8">
+        <v>130</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.2563</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" s="8">
+        <v>140</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.3071000000000002</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19" s="8">
+        <v>150</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2.3546</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20" s="8">
+        <v>160</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2.3933</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" s="8">
+        <v>170</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.4276</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" s="8">
+        <v>180</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2.4626999999999999</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" s="8">
+        <v>190</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2.4944000000000002</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" s="8">
+        <v>200</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2.5204</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="15:15" x14ac:dyDescent="0.2">
+      <c r="O37" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>